--- a/docs/コンペ質疑_質問票.xlsx
+++ b/docs/コンペ質疑_質問票.xlsx
@@ -55,7 +55,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -79,7 +79,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,7 +94,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -119,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -134,7 +139,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -146,10 +151,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -517,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -539,10 +547,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="52" customHeight="1">
+    <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。</t>
+          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。</t>
         </is>
       </c>
     </row>
@@ -620,959 +628,1184 @@
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
+          <t>★共0</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>宿題</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>C1/C2/D2</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>【共通宿題パック（3社同一様式で提出）】①ランク別単価×人数×稼働率%×期間の工数内訳マトリクスとWBSタスクとの対応表 ②当社想定成果物10点との対応表（成果物名・章レベル） ③「11月末RFP発行可能状態」の達成可否と、その前提条件・制約の一覧。</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Apple to Apple比較の土台。3社を同じ様式に載せて初めて価格・成果物・納期の採点(C1/C2/D2)が確定できる。</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>良: 3点すべて様式どおり提出。前提条件が具体的（当社の意思決定期限等）。
+危: 様式を無視した自社フォーマットでの回答、内訳の非開示、達成可否の留保つき回答。</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>（提出後の質疑で）内訳のうち最も工数を要するタスクはどれですか。そのタスクが計画超過した場合、どのタスクの工数を削って吸収しますか。</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>様式どおり提出いただけない項目について、開示できない理由を書面で示してください。開示なしの場合、該当採点項目は書面評価のまま確定します（低い素点で確定する旨を事前通告）。</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
           <t>共1</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>D1/D4</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>2028年1月に本番データ収集が始められないとしたら、その最大の原因は何だと考えますか。「1つだけ」挙げてください。そして、そのリスクは要件定義の何週目までに潰しますか。</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>ゴールからの逆算が本当にできているか。計画の美しさではなくクリティカルパスの理解を試す。</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>良: 自社作業ではなく「貴社側の意思決定」「保証人合意」「海外拠点データの実態」等、発注者側・外部の律速要因を名指しし、潰す期限が線表と整合。
 危: 「しっかりマネジメントします」等の一般論。リスクを複数並べて焦点をぼかす。</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>そのリスクの「兆候」は何のKPI・イベントで検知しますか。検知後のリカバリ策と、それでも間に合わない場合の縮退案（削る要件の優先順位）まで、事前に合意しておけますか。</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>では仮に「海外拠点の9月末データ回収が1ヶ月遅延」した場合、線表上どのタスクが何週間ずれ、11月末RFPに影響しますか。今この場で影響範囲を示してください。</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>共2</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Q5/D2</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>御社が過去に作成したRFPで、ベンダー各社の見積はどの程度ばらつきましたか。大きくばらついた、あるいは全社が一斉に高値・「個別見積り」で回答してきた経験はありますか。その原因と、本件RFPに組み込む再発防止策を教えてください。</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>本フェーズの成果物価値は「ベンダーが正確に・安く・比較可能に見積れるか」で決まる。RFPの出来をアウトカム（見積のばらつき）で語れるかを試す。</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>良: 実例の数字（N社中±○%）と原因分析（要件粒度・前提の曖昧さ・Must/Want未分別等）。
 危: 「弊社テンプレートは網羅的です」で終わる。失敗経験が「ない」（経験が浅いか不誠実）。</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>そのばらつきを抑えた仕掛け（要件の書き方・見積フォーマット・前提条件の固定方法）のうち、本件にそのまま流用できるものはどれですか。実物のサンプル（マスキング可）を提示できますか。</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>では本件で、ベンダー3社の見積を±20%以内に収める自信はありますか。収まらなかった場合、それは要件定義の品質問題です。御社はどう責任を取りますか（無償での要件明確化・再見積り支援等）。</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>共3</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Q3/D4</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>要件定義完了時点で「監査法人・SGSが証跡・統制要件に合意済み」という状態を作れますか。作れるなら、保証人といつ・何を・誰が協議するのか、線表上の具体的な位置を示してください。</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>後工程で最も高くつく手戻り＝保証人の「後出し」要求を、要件定義フェーズ内で予防する設計があるか。</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>良: 保証人協議をタスク・期日として線表に持ち、過去指摘一覧の反映方法まで語れる。
 危: 「保証対応も考慮した要件にします」（考慮と合意は別物）。</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>保証人が要件定義の途中で新たな証跡要求を出してきた場合、機能要件に反映するか業務運用で吸収するかの判断基準は何ですか。過去に「過剰統制」を回避した実例を1つ教えてください。</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>保証人との協議が線表にないのはなぜですか。協議なしで作った証跡要件が2028年度の限定保証で否認された場合、どの成果物のどの部分からやり直しになるか、影響を説明してください。</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8" ht="150" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>共4</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>C3/D2</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>本フェーズで御社が「やらないこと」を3つ挙げてください。また、11月末のRFP発行完了に間に合わなかった場合、追加費用なしで完遂まで対応することを契約に明記できますか。</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>スコープ規律（やらないことを明言できる会社は見積が正確）と、納期コミットの本気度を同時に試す。</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>良: やらないことが明確（ベンダー選定実務、戦略そのものの策定、保証実務等）で、遅延時の条件（無償継続 or 明確な免責条件）を即答。
 危: 「基本的に何でもご支援します」（見積に規律がない）。遅延条件への回答回避。</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>その「やらないこと」が途中で必要と判明した場合、誰が判断し、費用・期間はどう扱いますか。変更管理の手続き（申請→影響評価→合意）を契約書のどの条項でどう定義しますか。</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>「何でも支援する」なら、見積り工数の前提は何ですか。前提工数を超えた場合の扱い（吸収するのか、請求するのか、その閾値）を今この場で明文化してください。</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr"/>
-      <c r="J8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9" ht="150" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>共5</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>このプロジェクトが失敗するとしたら、御社ではなく当社側の原因として何が一番危ないですか。当社の誰の時間が、週に何時間必要ですか。</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>実行の解像度。要件定義の成否は発注者の意思決定速度で決まることを理解し、遠慮なく言える会社か。</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>良: 役職・部門を名指しで「意思決定者が週○時間」「Must/Should線引き合意が最初の関門」等、具体的な要求。
 危: 「貴社にはご負担をかけません」（請負型発想＝手戻りの温床）。</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>当社の意思決定が遅延した場合のエスカレーション設計（誰に・何日で・どう上げるか）は。最初の4週間で当社が決めるべき事項のリストを、優先順位つきで提示できますか。</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>「負担をかけない」なら、要件の確定判断は誰が行うのですか。当社が承認だけをする進め方で、11月末までに手戻りなく確定できる根拠を説明してください。</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>A社: ライズ・コンサルティングへの個別質問</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
+      <c r="I10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>★共6</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Q4/C4</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>本フェーズへの投資（御社見積額）は、①守り: 何を回避することで、②攻め: 何を生み出すことで回収されると説明しますか。それぞれ金額イメージつきで。そのうえで、その「攻め」は本フェーズの成果物（要件定義書・RFP）のどの章に、どんな具体的要件として現れますか。1つ例を挙げてください。</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>攻めが「構想の語り」で終わらず成果物に実装されるかの検証。守り(回避コスト)と攻め(創出価値)の両面でROIを語らせ、C4とQ4を同時に確定する全社比較の基準質問。</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>良: 回避コスト（監査工数・手戻り・選定失敗）と創出価値（CFP即応による受注維持等）を金額レンジで語り、攻め要件の実装先（例: データモデルの製品別粒度、KPI出力要件）を章レベルで即答。
+危: 攻めが「将来的には活用できます」で成果物に落ちない。ROIが定性論のみ。</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>その攻め要件が入ることで、システム構築費はいくら増えますか。増分投資を正当化する効果の試算は、いつ・誰が・どのデータで行いますか。</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>攻めの要件が成果物に1つも現れないなら、本フェーズの攻めは「構想止まり」であり、貴提案の攻めの訴求は本件スコープでは実体がないことになります。それでよいですか。</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr"/>
+      <c r="J11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>★共7</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Q1/Q3/Q4</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>守りと攻めの要件が衝突した場合——例えば、統制強化（証憑必須・多段階承認）が現場負荷やデータ活用のスピードを削ぐ場合——何を基準に、誰が、いつ裁定しますか。過去案件で実際に裁定した実例を1つ教えてください。</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>守り偏重（過剰統制で使われないシステム）にも攻め偏重（保証に耐えない基盤）にも倒れない「両利きの設計判断」ができるかの検証。本プロジェクトの本質的な緊張関係を理解しているかを試す。</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>良: 裁定基準（保証必須要件は不可侵、それ以外はリスクベースで統制水準を差別化等）と裁定者・タイミングを構造で語り、実例がある。
+危: 「両立します」（衝突の存在自体を認めない＝考えたことがない）。</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>本件で最初に衝突が起きそうな論点はどこだと予想しますか。その裁定を要件定義の何週目までに済ませるべきですか。</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>では具体例で伺います。海外拠点の証憑添付を全件必須にすると提出遅延が常態化する見込みの場合、証憑要件を緩めますか、期限を緩めますか、それとも別の解がありますか。今この場で判断プロセスを示してください。</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr"/>
+      <c r="J12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>A社: ライズ・コンサルティングへの個別質問</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>PMは田村様・豊田様のどちらですか。この場で確定してください。そのうえで、確定したPMご本人に伺います。難所③（ロジック実装）について、当社のExcelマクロ・R言語資産を「残す／移植する／作り直す」にどう仕分けるか、ご自身の言葉で進め方を説明してください。</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>「or」表記の解消と、実際に手を動かす人の実力の直接確認。資料の出来ではなく本人の頭で答えられるか。</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>良: PMを即確定し、本人が仕分け基準（再現性・保証要件・変更頻度等）を具体的に語る。
 危: 「受注後に最適な者を」と確定を避ける。本人が答えられず同席者が代弁する。</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>その仕分けで「作り直す」と判定されたロジックは、誰が・どのフェーズで作り直すのですか。本フェーズの成果物（機能要件）にはどの粒度で反映されますか。</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>確定できないなら、契約書に「PM候補2名のうち当社が指名できる」と記載できますか。あわせて両名の直近3ヶ月の他案件稼働状況を開示してください。</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr"/>
-      <c r="J11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>定価3,520万円から32%の値引きの原資は何ですか（稼働を削るのか、単価を下げるのか、投資と割り切るのか）。値引き後単価は設計フェーズ以降も維持されますか。ランク別単価×人数×稼働率×期間の内訳を提出してください。</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>採点ルール上の「極端な安値の実態確認」。入口価格で次フェーズから単価を戻すモデルなら総コストで逆転する。</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>良: 内訳を開示し、次フェーズ単価も数字で明言。
 危: 次フェーズ単価の明言を避ける。「戦略的価格です」のみで内訳非開示。</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>次フェーズ（設計・開発PMO）の想定単価表を提示してください。この単価で、御社の品質管理（AP層のレビュー工数）は週何時間確保されますか。</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>値引き前提の稼働計画で要件定義が難航（工数超過）した場合、真っ先に削られるのはどの作業ですか。品質管理・レビュー工数を削らないことを、どう保証しますか。</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr"/>
-      <c r="J12" s="10" t="inlineStr"/>
-    </row>
-    <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>SSBJ／第三者保証／非財務データ基盤の類似案件について、会社としての実績を「社名・時期・御社の役割・定量成果」の4点セットで3件、提出してください。守秘義務で社名が出せない場合は、業種・売上規模・拠点数で特定可能な粒度まで。</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>個人経歴頼みの実績を「会社の能力」として検証する。3件出せなければQ5素点2を確定。</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>良: 4点セットで3件、役割が主体的（PMO・要件定義リード）。
 危: 個人の過去所属時代の実績を会社実績のように語る。役割が「支援・参画」のみ。</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>その3件のうち、想定通りに行かなかった点（失敗）と、本件に持ち込む回避策を各1つずつ教えてください。</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>会社実績が乏しい場合、SSBJ基準の解釈（例: 産業横断指標・セーフハーバーの扱い）は誰の知見で担保しますか。外部専門家を使うなら、その費用は見積りに含まれていますか。</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr"/>
-      <c r="J13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr"/>
+      <c r="J16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>「条件付き要件」を含むRFPに対して、ベンダーは通常リスクバッファを乗せるか「個別見積り」で回答してきます。条件付き要件を含むRFPで、実際にベンダーから比較可能な固定見積りを取れた事例はありますか。取れなかった場合、当社のベンダー選定は何を基準に行うことになりますか。</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>提案の中核方法論のアウトカム検証。「RFPは書けるがベンダーが値付けできない」なら本末転倒。</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>良: 事例があり、変動幅×段階見積り（ベース＋オプション）等の具体的な工夫を語れる。
 危: 「ベンダーと調整します」。事例なし＋対策も一般論。</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>条件付き要件の「変動幅」は誰がどう見積るのですか。変動幅ごとの段階見積りを求めるRFPフォーマットのサンプル（マスキング可）を提示できますか。</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>事例がないなら、ベンダーが高値バッファを乗せるリスクをどう抑えますか。RFP発出前のベンダー事前サウンディングを実施しますか。実施する場合、誰の工数で・本見積りに含まれていますか。</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr"/>
-      <c r="J14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>A5</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>御社成果物（要件定義書3点＋RFP本紙＋評価要領）と当社想定成果物10点の対応表を提出してください。特に「海外拠点拡張ロードマップ」「グローバルデータ収集要件書」はどの成果物のどの章で担保されますか。</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>成果物カバレッジの検証。「4文書に集約」の裏で当社要求が薄まっていないか。</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>良: 10点すべてに章レベルの対応があり、粒度差も自己申告。
 危: 対応表が「概ね含まれます」レベルで章の特定がない。</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>対応表で「一部含む」となる成果物について、当社想定粒度との差分を埋める場合の追加工数・費用を提示してください。</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>海外拠点拡張ロードマップが成果物にないのは「スコープ外」という理解でよいですか。含める場合の金額・期間影響を提示してください。</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr"/>
-      <c r="J15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr"/>
+      <c r="J18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>★A6</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Q4/C4</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>貴提案の攻めは「可視化・活用の初期仮説」までで、PBR向上・受注拡大への定量接続が見えません。CFP即応・削減貢献量といった当社の攻めユースケースを、要件定義期間中に「どの部門から・何のデータを取り・どの成果物に・どんな要件として」確定させるのか、進め方を具体的に説明してください。</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>書面でQ4素点3（一般論止まり）のA社に挽回機会を与え、攻め能力の実体を確認する。3社の攻めを同じ土俵で比較するための質問。</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>良: 当社の事業構造（Cat11・製品別原単位等）を踏まえ、ヒアリング先・必要データ・成果物への落とし込みを具体的に語れる。
+危: 「貴社と議論しながら決めます」（進め方の設計がない＝攻めは他社材料の後追い）。</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>削減貢献量（Scope4）は算定基準が確立していません。前提条件と算定方法の妥当性を、社外（投資家・顧客）にどう説明可能な形で要件化しますか。</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>攻めの要件化経験が乏しいなら、本件では守り（開示・保証）に集中し、攻めは初期仮説の提示までと割り切る提案と理解してよいですか。その場合の見積り減額余地はありますか。</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>B社: PwCコンサルティングへの個別質問</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="150" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>宿題+即答</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>100%稼働の実働3名（SA/A）の実名・経歴・類似案件経験を提示してください。提示できない場合、御社の品質保証は「SM20%のレビュー」に依存することになりますが、ジュニア3名の成果物をレビュー20%で品質担保できた同型案件の実例を示してください。</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>書面最大の弱点。実名が出ないなら「誰が来るか分からない提案」としてQ6素点2を確定させる。</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>良: 3名の実名・経歴・類似経験を提示。
 危: 「受注後にベストな人材を」＝アサイン未確定の証左。実例なしで「品質プロセスがあるので大丈夫」。</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>（実名が出た場合）3名の直近案件と本件との類似性、11月末までの他案件重複を開示してください。1名でも交代する場合の事前通知と当社承認プロセスを契約に入れられますか。</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>実名が出せないのは社内でアサインが確定していないからですか。それは受注後「集められる人で始める」ことを意味しませんか。キックオフ時点で確定している保証（確約書等）を出せますか。</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22" ht="150" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>D1/D2</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>線表はRFP発出12月末（仮）ですが、当社の要求は11月末です。前倒しは可能ですか。可能なら「何を削るか・体制をどう変えるか・金額はいくら変わるか」。不可能なら、その1ヶ月遅れが後続のベンダー選定〜2028年1月本番収集の逆線表にどう影響するか、御社の見解を示してください。</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>要求期限とのズレの認識確認。根拠なき「できます」も、理由曖昧な「できません」も減点。</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>良: 前倒し案が具体的（削るタスク・増員・金額差）か、12月末で間に合う逆線表を数字で示す。
 危: 「頑張ります」。逆線表なしの「問題ありません」。</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>前倒しのために削る作業は、後続フェーズのどこで・誰が・いくらで実施することになりますか（先送りの総コストを提示してください）。</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>12月末発出だと、ベンダーの提案期間が年末年始を挟みます。提案品質・参加意欲への影響と、当社の評価・稟議期間を含めて2028年1月に間に合う根拠を、週単位の逆線表で示してください。</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr"/>
-      <c r="J18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19" ht="150" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Q4/中立性</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>御社はNet Zero Cloud Partner of the Yearであり、自社アセット（PwC Net Zeroアセット）もお持ちです。本件RFPの評価軸設計において、Salesforce系ソリューションが構造的に有利になるバイアスをどう排除しますか。過去のツール選定支援で、御社の導入実績がないツールが選定された事例はありますか。</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>RFP作成者のバイアスは要件の書き方に必ず現れる。実例で中立性を証明できるか。</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>良: 実例＋プロセス上の仕掛け（評価軸の貴社承認、製品非依存の要件記述等）。
 危: 「中立に評価します」の宣言のみ。実例なし。</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>評価軸の設計に、当社＋第三者（御社と利害関係のない専門家）のレビューを入れることに同意しますか。PwC Net Zeroアセットを本件の候補から除外することは可能ですか。</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>導入実績のないツールが選ばれた事例がないなら、それは御社のRFPが実績あるツールに最適化されている証左ではありませんか。機能要件を製品非依存で記述する具体的な方法（記述例）を示してください。</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20" ht="150" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>C3/Q2</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>御社提案は「ルール策定・算定ロジックは当社にて策定済み」を前提としています。要件定義開始後にこの前提が崩れていた（未策定・不十分と判明した）場合、追加費用と期間影響はどうなりますか。契約前に条件を明文化できますか。</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>最も楽観的な前提を置いた提案。変更管理の実運用を契約条件レベルで確定させる。</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>良: 前提検証の方法と、崩れた場合の費用・期間の扱いを具体的に提示。
 危: 「その際はご相談」のみで基準なし。</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>最初の2週間のAs-Is確認で前提を検証するチェックリストを提示できますか。「策定済み」と判定する基準を契約前に当社と合意しましょう。</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>再見積りとなる場合の適用単価と、期間延長時の11月末（当社要求）への影響を試算してください。前提リスクを織り込んだ固定価格案を提示できますか。</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="10" t="inlineStr"/>
-    </row>
-    <row r="21" ht="150" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25" ht="150" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>将来予測・Scope3一次データ化をStep2以降とされていますが、今回のRFPに拡張性要件として織り込まなければ、Step2で基盤の作り直しが発生しませんか。Step2を見据えて今回のRFPに最低限入れるべき要件を、この場で3つ挙げてください。</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>「後ろ倒し」の設計思想が手戻りリスクを内包していないかの検証。</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>良: データモデル・API・マスタ構造など基盤側に効く拡張性要件を即答。
 危: 「Step2で改めて検討」（＝作り直し容認）。</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>その3つの要件はRFPでMust要件にしますか、評価加点にしますか。Must化した場合の初期構築コストへの影響見立てを教えてください。</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>Step2で基盤を作り直した事例・作り直さずに済んだ事例を各1つ挙げ、何が分かれ目だったかを説明してください。</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>C社: アビームコンサルティングへの個別質問</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="150" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>「9〜11月・当社想定成果物10点・11月末RFP発行可能状態」を基準スコープとした場合の切り出し金額を、ランク別単価×人数×稼働率×期間の内訳付きで提出してください。ベンダー評価支援・非システム課題ロードマップ・効果試算はオプション別価格として分離してください。なお、内部統制・保証対応論点整理（貴提案タスク#12）と攻めユースケースの要件化は基準スコープに含めてください。</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>7,800万円の検証可能化。#12とユースケース要件化を基準側に残すのは、外すと品質（Q3/Q4）の裏付けが消えるため。</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>良: 内訳つきで切り出しに応じ、オプション価格も明示。
 危: 「一体でこそ価値がある」と分解を拒む（検証拒否と同義）。</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>切り出し後もなお他社比で高い場合、その差は体制の厚みと理解します。本件の品質を左右する上位3リスクについて、その厚い体制が「他社では起きる問題をどう防ぐか」を具体的に説明してください。</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>内訳が出せない理由は何ですか。準委任契約で工数内訳が開示できないのは説明がつきません。開示なしで7,800万円の妥当性を当社はどう検証すればよいのですか。</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28" ht="150" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>RFP発行「年内」を11月末に前倒しできますか。ボトルネックは何ですか。前倒しのために当社が9月中に意思決定すべき事項を、優先順位付きで挙げてください。</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>2028/1逆算を掲げる同社が「12月で間に合う」と考えるなら、その根拠を数字で語らせる。合理的なら当社計画の見直し材料にもなる。</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>良: 前倒しの条件（当社の意思決定期限・削る要素）を具体的に提示、または12月案の合理性を逆線表で証明。
 危: 「調整可能です」のみ。ボトルネックを特定できない。</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>11月末発行の前倒し案において、当社が9月中に決められなかった場合の縮退ルール（どの要件を条件付きに落とすか）を事前合意できますか。</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>「12月で間に合う」根拠の逆線表で、ベンダー評価が1月末に完了しなかった場合（回答遅延・再質疑）のバッファはどこにありますか。2027年中構築完了のクリティカルパスには何日の余裕がありますか。</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>中立性</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>御社はベンダー評価・選定までをスコープに含め、ソリューションベンダーとのリレーションを強みとして挙げています。後続の導入フェーズを御社自身が受注する意思はありますか。ある場合、要件定義・RFP・評価軸が御社の得意なソリューションや自社導入体制に有利に働かないことをどう担保しますか。</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>「RFPを書く者が選定も行い、導入も狙う」構造は最も利益相反が起きやすい。導入受注の意思を先に言質として取る。</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>良: 受注意思の有無を明言し、ある場合は評価から自社を外す設計に同意。
 危: 「その時点で検討」（意思を曖昧にしたまま選定に関与し続ける）。</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>導入を受注しないと明言できるなら、それを契約書（入札制限条項）に明記できますか。受注可能性を残すなら、ベンダー評価プロセスから御社を外し「当社＋第三者評価」とする設計に同意しますか。</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>「中立評価」の実績として、御社リレーション外のベンダーが選定された割合を開示してください。RFP発出先リストの選定基準は誰が作り、誰が承認しますか。</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26" ht="150" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30" ht="150" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>「参画メンバーは変更になる可能性があります」の注記を撤回し、主要5名（豊嶋・山野・平野・張本・今野の各氏）の稼働率%・期間中の交代禁止（または交代時の品質担保条件）を確約できますか。また、SGホールディングス案件等、同時期に走る大型案件との要員重複はありませんか。</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>実名の豪華さと実際の稼働は別物。特にプリンシパル・ダイレクター級の実稼働%を数字で確定させる。</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>良: 月別稼働率%と交代条件を書面で確約。重複を正直に開示。
 危: 注記を維持したまま「基本的には変わりません」。アドバイザーの稼働が「適宜」のまま。</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>プリンシパル・ダイレクター級は実質週何時間を本件に使いますか。定例会議出席以外の実働（成果物レビュー時間）をコミットできますか。</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>注記を撤回できない理由は何ですか。交代時に「同等以上のランク・類似経験者を当社承認のうえ配置」する条項を契約に入れられますか。</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27" ht="150" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31" ht="150" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>C4/Q4</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>「工数削減額・リスク回避額・収益機会」の効果3分類について、過去案件で経営会議が実際に投資承認した試算の実例を1件、数字の粒度が分かる形で紹介してください（社名は伏せて構いません）。「CFP即応が受注シェアに直結」という仮説の根拠となるデータはありますか。</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>攻めのストーリーが「営業トーク」か「再現可能な方法論」かの見極め。</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>良: 実例の試算構造（前提・データソース・金額規模）を具体的に説明。
 危: フレームワークの説明に終始し実例が出ない。</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>その実例の試算ロジックを本件に適用した場合、当社のROI試算はいつ時点で・どの精度で出せますか。当社の経営上申（投資承認）のタイミングとどう整合させますか。</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>実例が出せないなら、効果3分類は概念に留まります。数億円規模になる基盤構築の投資判断を支える定量根拠を、この要件定義期間中に・どのデータで作るのか説明してください。</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32" ht="150" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>★C6</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Q2/Q5</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>「戦略依存×Must/Should/Could」の4象限と二層整理（共通要件＋テーマ別シナリオ）を適用した過去案件で、①線引きの判断が貴社とクライアントで割れた実例と収拾方法、②戦略確定後に実際にRFP要件がどれだけ変わったか（変更件数・変更率）を教えてください。</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>書面で最高評価（Q2素点5）をつけた中核方法論の実効性検証。素点5は「裏付け完全」が要件のため、高得点ほど質疑での検証が必須。方法論が本当に手戻りを減らしたのかをアウトカム（変更率）で証明させる。</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>良: 割れた実例を率直に語り、変更率を数字で示せる（例: 戦略確定後の要件変更が全体の○%に収まり、うち構造変更はゼロ等）。
+危: 「うまくいきました」のみで数字なし。割れた実例が「ない」（適用実績が浅いか、都合の悪い情報を出さない）。</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>本件でMust×戦略非依存の「骨格」に置くと仰る組織マスタ・証憑統制・Scope1/2算定のうち、実は当社の戦略次第で動き得るものはどれですか。骨格の線引きを最初の何週で当社と合意しますか。</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>変更率のデータがないなら、「手戻り最小化」の効果は測定されていない主張になります。本件では何をもって「手戻りが最小化された」と評価すればよいか、測定可能な形で定義してください。</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A26:J26"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A13:J13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/コンペ質疑_質問票.xlsx
+++ b/docs/コンペ質疑_質問票.xlsx
@@ -918,7 +918,8 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>攻めが「構想の語り」で終わらず成果物に実装されるかの検証。守り(回避コスト)と攻め(創出価値)の両面でROIを語らせ、C4とQ4を同時に確定する全社比較の基準質問。</t>
+          <t>攻めが「構想の語り」で終わらず成果物に実装されるかの検証。守り(回避コスト)と攻め(創出価値)の両面でROIを語らせ、C4とQ4を同時に確定する全社比較の基準質問。
+【会社別の入り方】C社アビームは主質問の大半に書面回答済み(P.20-21の4象限・基盤要件化、P.28ユースケース評価)のため、「書面は承知」と前置きして主質問を飛ばし深掘り①から入る(書面でも金額イメージと構築費増分は未回答)。数字で答えればQ4/C4は4→5の可能性、答えられなくても書面裏付けがあるため4維持。A社・B社は主質問から入り、書面で示せていない攻めの補完・挽回機会とする。</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/コンペ質疑_質問票.xlsx
+++ b/docs/コンペ質疑_質問票.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。</t>
+          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検（第1回）で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。⑦アビームv1.1改訂（基本/オプション分離）と成果物カバレッジ照合（第2回再点検）を反映しC1・★A7・★B6・★C7を追加/更新。スコープ差は双方向（アビームが広い部分／PwC案②が広い部分の両方が存在）のため、価格差を単純にスコープや品質だけで説明させない設計。</t>
         </is>
       </c>
     </row>
@@ -1272,267 +1272,296 @@
       <c r="I19" s="10" t="inlineStr"/>
       <c r="J19" s="10" t="inlineStr"/>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>★A7</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>宿題+即答</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>C1/D2</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>貴社の成果物一覧（業務・機能・非機能要件定義書＋RFP本紙）を照合したところ、独立したシステム構成図（アーキテクチャ）、独立したデータ要件定義書、ユースケースの優先順位付け（効果×実現性評価）が明示されていません。①これらは非機能要件定義書等に含まれる想定ですか、それとも本提案のスコープ外ですか。②スコープ外の場合、追加した場合の金額・期間影響を提示してください。</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>貴社の安さ（2,400万円）の一部は正当なスコープの狭さで説明できるはずだが、それを定量化する。安さが「効率」か「手抜き」かをこの回答で判別する。</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>良: 現在の成果物のどこに何が含まれるかを明確に切り分け、不足分の追加金額を具体的に提示。
+危: 「含まれています」と主張するが、成果物一覧のどの記載か特定できない。</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>アーキテクチャ図がないままRFPを発行した場合、ベンダー各社の提案アーキテクチャが比較できず、評価が長期化するリスクがあります。このリスクをどう考えますか。</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>含まれていないなら、貴社の2,400万円はPwC社の27,000,000円やアビーム社の基本スコープと同じ土俵で比較できません。追加金額を示せないなら、当社は貴社の見積りをそのままでは採用できません。</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>B社: PwCコンサルティングへの個別質問</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="150" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="150" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>宿題+即答</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>100%稼働の実働3名（SA/A）の実名・経歴・類似案件経験を提示してください。提示できない場合、御社の品質保証は「SM20%のレビュー」に依存することになりますが、ジュニア3名の成果物をレビュー20%で品質担保できた同型案件の実例を示してください。</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>書面最大の弱点。実名が出ないなら「誰が来るか分からない提案」としてQ6素点2を確定させる。</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>良: 3名の実名・経歴・類似経験を提示。
 危: 「受注後にベストな人材を」＝アサイン未確定の証左。実例なしで「品質プロセスがあるので大丈夫」。</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>（実名が出た場合）3名の直近案件と本件との類似性、11月末までの他案件重複を開示してください。1名でも交代する場合の事前通知と当社承認プロセスを契約に入れられますか。</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>実名が出せないのは社内でアサインが確定していないからですか。それは受注後「集められる人で始める」ことを意味しませんか。キックオフ時点で確定している保証（確約書等）を出せますか。</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22" ht="150" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>D1/D2</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>線表はRFP発出12月末（仮）ですが、当社の要求は11月末です。前倒しは可能ですか。可能なら「何を削るか・体制をどう変えるか・金額はいくら変わるか」。不可能なら、その1ヶ月遅れが後続のベンダー選定〜2028年1月本番収集の逆線表にどう影響するか、御社の見解を示してください。</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>要求期限とのズレの認識確認。根拠なき「できます」も、理由曖昧な「できません」も減点。</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>良: 前倒し案が具体的（削るタスク・増員・金額差）か、12月末で間に合う逆線表を数字で示す。
 危: 「頑張ります」。逆線表なしの「問題ありません」。</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>前倒しのために削る作業は、後続フェーズのどこで・誰が・いくらで実施することになりますか（先送りの総コストを提示してください）。</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>12月末発出だと、ベンダーの提案期間が年末年始を挟みます。提案品質・参加意欲への影響と、当社の評価・稟議期間を含めて2028年1月に間に合う根拠を、週単位の逆線表で示してください。</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-    </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Q4/中立性</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>御社はNet Zero Cloud Partner of the Yearであり、自社アセット（PwC Net Zeroアセット）もお持ちです。本件RFPの評価軸設計において、Salesforce系ソリューションが構造的に有利になるバイアスをどう排除しますか。過去のツール選定支援で、御社の導入実績がないツールが選定された事例はありますか。</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>RFP作成者のバイアスは要件の書き方に必ず現れる。実例で中立性を証明できるか。</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>良: 実例＋プロセス上の仕掛け（評価軸の貴社承認、製品非依存の要件記述等）。
 危: 「中立に評価します」の宣言のみ。実例なし。</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>評価軸の設計に、当社＋第三者（御社と利害関係のない専門家）のレビューを入れることに同意しますか。PwC Net Zeroアセットを本件の候補から除外することは可能ですか。</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>導入実績のないツールが選ばれた事例がないなら、それは御社のRFPが実績あるツールに最適化されている証左ではありませんか。機能要件を製品非依存で記述する具体的な方法（記述例）を示してください。</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25" ht="150" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>C3/Q2</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>御社提案は「ルール策定・算定ロジックは当社にて策定済み」を前提としています。要件定義開始後にこの前提が崩れていた（未策定・不十分と判明した）場合、追加費用と期間影響はどうなりますか。契約前に条件を明文化できますか。</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>最も楽観的な前提を置いた提案。変更管理の実運用を契約条件レベルで確定させる。</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>良: 前提検証の方法と、崩れた場合の費用・期間の扱いを具体的に提示。
 危: 「その際はご相談」のみで基準なし。</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>最初の2週間のAs-Is確認で前提を検証するチェックリストを提示できますか。「策定済み」と判定する基準を契約前に当社と合意しましょう。</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>再見積りとなる場合の適用単価と、期間延長時の11月末（当社要求）への影響を試算してください。前提リスクを織り込んだ固定価格案を提示できますか。</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26" ht="150" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>将来予測・Scope3一次データ化をStep2以降とされていますが、今回のRFPに拡張性要件として織り込まなければ、Step2で基盤の作り直しが発生しませんか。Step2を見据えて今回のRFPに最低限入れるべき要件を、この場で3つ挙げてください。</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>「後ろ倒し」の設計思想が手戻りリスクを内包していないかの検証。</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>良: データモデル・API・マスタ構造など基盤側に効く拡張性要件を即答。
 危: 「Step2で改めて検討」（＝作り直し容認）。</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>その3つの要件はRFPでMust要件にしますか、評価加点にしますか。Must化した場合の初期構築コストへの影響見立てを教えてください。</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>Step2で基盤を作り直した事例・作り直さずに済んだ事例を各1つ挙げ、何が分かれ目だったかを説明してください。</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>C社: アビームコンサルティングへの個別質問</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
+      <c r="I26" s="10" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr"/>
     </row>
     <row r="27" ht="150" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>C1</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>★B6</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -1547,265 +1576,371 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>「9〜11月・当社想定成果物10点・11月末RFP発行可能状態」を基準スコープとした場合の切り出し金額を、ランク別単価×人数×稼働率×期間の内訳付きで提出してください。ベンダー評価支援・非システム課題ロードマップ・効果試算はオプション別価格として分離してください。なお、内部統制・保証対応論点整理（貴提案タスク#12）と攻めユースケースの要件化は基準スコープに含めてください。</t>
+          <t>御見積書の案②（27,000,000円）には「1-4 業務要件定義書作成」1タスクのみが業務要件側の記載ですが、当社が別途照合したところ、機能要件定義書・データ要件定義書・システム要件定義書に相当する独立した記載が価格表上で確認できません。①これらは1-4に含まれますか、②含まれないなら追加のタスク・金額が必要ですか、を明確にしてください。</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>7,800万円の検証可能化。#12とユースケース要件化を基準側に残すのは、外すと品質（Q3/Q4）の裏付けが消えるため。</t>
+          <t>27,000,000円が3社中最も割安に見えるが、実は機能/データ/システム要件の独立文書化が価格表に見えないだけかもしれない。曖昧なまま比較すると不当にPwCを過大評価するリスクがあるため、この場で解消する。</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>良: 内訳つきで切り出しに応じ、オプション価格も明示。
-危: 「一体でこそ価値がある」と分解を拒む（検証拒否と同義）。</t>
+          <t>良: 1-4の範囲を明確に定義し、含まれる場合はその粒度（アビームの#6〜#8相当か）を具体的に示す。含まれない場合は金額を明示。
+危: 「業務要件定義書に含まれます」で粒度の説明がない。</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>切り出し後もなお他社比で高い場合、その差は体制の厚みと理解します。本件の品質を左右する上位3リスクについて、その厚い体制が「他社では起きる問題をどう防ぐか」を具体的に説明してください。</t>
+          <t>機能要件定義書を独立文書として発行することは可能ですか。その場合、貴社の成果物マッピング表（P.40）に記載の「システム機能要求一覧」等との対応関係を教えてください。</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>内訳が出せない理由は何ですか。準委任契約で工数内訳が開示できないのは説明がつきません。開示なしで7,800万円の妥当性を当社はどう検証すればよいのですか。</t>
+          <t>含まれないなら、案②の27,000,000円は当社が想定する成果物10点を満たしていない可能性があります。満たすための追加金額を今この場で概算で示してください。</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr"/>
       <c r="J27" s="10" t="inlineStr"/>
     </row>
-    <row r="28" ht="150" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>C社: アビームコンサルティングへの個別質問</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>宿題</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>C1/C2</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>【v1.1反映】基本スコープ5,300万円（オプションA/B分離済み）について、ランク別単価×人数×稼働率×期間の内訳を提出してください。あわせて、基本スコープの各タスク（#1〜#10、#12の一部）と内訳の対応表を示し、どのタスクに最も工数を要しているかを明示してください。</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>分離自体は完了済みだが、なお5,300万円が他社の1.6〜2.2倍である原因が「単価水準」か「投入人数・稼働率」かは、この内訳でしか切り分けられない。</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>良: 内訳つきで提出し、単価が他社と同水準（品質差で説明できる）か、単価自体が高い（品質と無関係な割高要因）かが判別できる。
+危: 総額のみで内訳を示さない、又はタスク対応が粗い。</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>最も工数を要するタスクはどれですか。そのタスクが期間内に完了しなかった場合、どのタスクの工数を削って吸収しますか。</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>内訳が出せない理由は何ですか。準委任契約で工数内訳が開示できないのは説明がつきません。開示なしで5,300万円の妥当性を当社はどう検証すればよいのですか。</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30" ht="150" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>RFP発行「年内」を11月末に前倒しできますか。ボトルネックは何ですか。前倒しのために当社が9月中に意思決定すべき事項を、優先順位付きで挙げてください。</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>2028/1逆算を掲げる同社が「12月で間に合う」と考えるなら、その根拠を数字で語らせる。合理的なら当社計画の見直し材料にもなる。</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>良: 前倒しの条件（当社の意思決定期限・削る要素）を具体的に提示、または12月案の合理性を逆線表で証明。
 危: 「調整可能です」のみ。ボトルネックを特定できない。</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>11月末発行の前倒し案において、当社が9月中に決められなかった場合の縮退ルール（どの要件を条件付きに落とすか）を事前合意できますか。</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>「12月で間に合う」根拠の逆線表で、ベンダー評価が1月末に完了しなかった場合（回答遅延・再質疑）のバッファはどこにありますか。2027年中構築完了のクリティカルパスには何日の余裕がありますか。</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr"/>
-      <c r="J28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29" ht="150" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31" ht="150" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>中立性</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>御社はベンダー評価・選定までをスコープに含め、ソリューションベンダーとのリレーションを強みとして挙げています。後続の導入フェーズを御社自身が受注する意思はありますか。ある場合、要件定義・RFP・評価軸が御社の得意なソリューションや自社導入体制に有利に働かないことをどう担保しますか。</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>「RFPを書く者が選定も行い、導入も狙う」構造は最も利益相反が起きやすい。導入受注の意思を先に言質として取る。</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>良: 受注意思の有無を明言し、ある場合は評価から自社を外す設計に同意。
 危: 「その時点で検討」（意思を曖昧にしたまま選定に関与し続ける）。</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>導入を受注しないと明言できるなら、それを契約書（入札制限条項）に明記できますか。受注可能性を残すなら、ベンダー評価プロセスから御社を外し「当社＋第三者評価」とする設計に同意しますか。</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>「中立評価」の実績として、御社リレーション外のベンダーが選定された割合を開示してください。RFP発出先リストの選定基準は誰が作り、誰が承認しますか。</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30" ht="150" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32" ht="150" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>「参画メンバーは変更になる可能性があります」の注記を撤回し、主要5名（豊嶋・山野・平野・張本・今野の各氏）の稼働率%・期間中の交代禁止（または交代時の品質担保条件）を確約できますか。また、SGホールディングス案件等、同時期に走る大型案件との要員重複はありませんか。</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>実名の豪華さと実際の稼働は別物。特にプリンシパル・ダイレクター級の実稼働%を数字で確定させる。</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>良: 月別稼働率%と交代条件を書面で確約。重複を正直に開示。
 危: 注記を維持したまま「基本的には変わりません」。アドバイザーの稼働が「適宜」のまま。</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>プリンシパル・ダイレクター級は実質週何時間を本件に使いますか。定例会議出席以外の実働（成果物レビュー時間）をコミットできますか。</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>注記を撤回できない理由は何ですか。交代時に「同等以上のランク・類似経験者を当社承認のうえ配置」する条項を契約に入れられますか。</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr"/>
-      <c r="J30" s="10" t="inlineStr"/>
-    </row>
-    <row r="31" ht="150" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33" ht="150" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>C4/Q4</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>「工数削減額・リスク回避額・収益機会」の効果3分類について、過去案件で経営会議が実際に投資承認した試算の実例を1件、数字の粒度が分かる形で紹介してください（社名は伏せて構いません）。「CFP即応が受注シェアに直結」という仮説の根拠となるデータはありますか。</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>攻めのストーリーが「営業トーク」か「再現可能な方法論」かの見極め。</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>良: 実例の試算構造（前提・データソース・金額規模）を具体的に説明。
 危: フレームワークの説明に終始し実例が出ない。</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>その実例の試算ロジックを本件に適用した場合、当社のROI試算はいつ時点で・どの精度で出せますか。当社の経営上申（投資承認）のタイミングとどう整合させますか。</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>実例が出せないなら、効果3分類は概念に留まります。数億円規模になる基盤構築の投資判断を支える定量根拠を、この要件定義期間中に・どのデータで作るのか説明してください。</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32" ht="150" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34" ht="150" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>★C6</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>即答</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Q2/Q5</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>「戦略依存×Must/Should/Could」の4象限と二層整理（共通要件＋テーマ別シナリオ）を適用した過去案件で、①線引きの判断が貴社とクライアントで割れた実例と収拾方法、②戦略確定後に実際にRFP要件がどれだけ変わったか（変更件数・変更率）を教えてください。</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>書面で最高評価（Q2素点5）をつけた中核方法論の実効性検証。素点5は「裏付け完全」が要件のため、高得点ほど質疑での検証が必須。方法論が本当に手戻りを減らしたのかをアウトカム（変更率）で証明させる。</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t>良: 割れた実例を率直に語り、変更率を数字で示せる（例: 戦略確定後の要件変更が全体の○%に収まり、うち構造変更はゼロ等）。
 危: 「うまくいきました」のみで数字なし。割れた実例が「ない」（適用実績が浅いか、都合の悪い情報を出さない）。</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>本件でMust×戦略非依存の「骨格」に置くと仰る組織マスタ・証憑統制・Scope1/2算定のうち、実は当社の戦略次第で動き得るものはどれですか。骨格の線引きを最初の何週で当社と合意しますか。</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>変更率のデータがないなら、「手戻り最小化」の効果は測定されていない主張になります。本件では何をもって「手戻りが最小化された」と評価すればよいか、測定可能な形で定義してください。</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr"/>
+      <c r="I34" s="10" t="inlineStr"/>
+      <c r="J34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35" ht="150" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>★C7</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>C1/C2</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>当社にて成果物を照合したところ、PwC社の27,000,000円の見積り（3.6ヶ月）には「開示効率化検討」「展開計画・定着計画」「PJ計画書」が含まれていますが、貴社の基本スコープ5,300万円（3.9ヶ月）にはこれらが含まれず、オプションBに切り出されています。つまり貴社の基本スコープは他社より成果物が狭いにもかかわらず、価格はPwC社の約2倍です。この差の主因は単価水準ですか、投入人数ですか。ランク別内訳（C1の宿題回答）でご説明ください。</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>最も鋭い一問。品質でもスコープでも説明のつかない価格差（超過コスト）を、貴社自身に他社比較で直接答えさせる。回避不能な形で単価水準の説明責任を負わせる。</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>良: 単価が他社より高い理由を明確に説明（シニアリティ、専門性、リスクプレミアム等）し、その根拠を具体的な数字・実例で示す。
+危: 「価値が違います」等の定性論で数字を出さない。他社見積りの前提を問題にして自社の説明を回避する。</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>その単価差に見合う成果（例: 手戻りゼロ、保証人指摘ゼロ）を過去案件で実現した実例はありますか。本件でその成果を測定可能な形で契約に落とし込めますか。</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>説明できないなら、貴社の基本スコープ価格は市場価格から外れている可能性があります。PwC社の27,000,000円の内容に貴社の強み（2段階アーキテクチャ・独立データ要件定義書）を追加した場合の増分見積りを、この場で概算で示してください。</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A21:J21"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A26:J26"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A28:J28"/>
     <mergeCell ref="A13:J13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/コンペ質疑_質問票.xlsx
+++ b/docs/コンペ質疑_質問票.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検（第1回）で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。⑦アビームv1.1改訂（基本/オプション分離）と成果物カバレッジ照合（第2回再点検）を反映しC1・★A7・★B6・★C7を追加/更新。スコープ差は双方向（アビームが広い部分／PwC案②が広い部分の両方が存在）のため、価格差を単純にスコープや品質だけで説明させない設計。</t>
+          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検（第1回）で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。⑦アビームv1.1改訂（基本/オプション分離）と成果物カバレッジ照合（第2回再点検）を反映しC1・★A7・★B6・★C7を追加/更新。スコープ差は双方向（アビームが広い部分／PwC案②が広い部分の両方が存在）のため、価格差を単純にスコープや品質だけで説明させない設計。⑧第3回再点検: アサインメンバーの経歴を「攻め／守り」の技術専門性（システム連携・API連携経験等）で照合し、★共8・★A8・★B7・★C8を追加。Q6は実名・経歴の有無までしか採点していないため、本件の技術判断に耐える経験の有無と、その人物が実働で入るか（アドバイザー止まりでないか）を別途確認する。</t>
         </is>
       </c>
     </row>
@@ -986,962 +986,1142 @@
       <c r="I12" s="10" t="inlineStr"/>
       <c r="J12" s="10" t="inlineStr"/>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>★共8</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Q3/Q4/Q6</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>本件のシステム連携・アーキテクチャ設計（既存システム＝ERP・環境管理システム等との接続方式決定、証跡・ワークフローの実装可能性検証）を技術的に主導するのは誰ですか。その方が過去に主導した「システム連携を伴う要件定義」の実例を、連携方式（API／CSV／ファイル連携等）と規模（拠点数・システム数）で教えてください。また、攻めのデータ活用設計（KPI・BI・分析基盤の要件化）を主導するのは誰ですか、同様に実例を教えてください。守り担当と攻め担当は同一人物ですか、分離していますか。</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Q6は「実名・経歴の有無」までしか採点していない。ここでは実名の中身——本件の技術判断（証跡ワークフロー実装可否・API連携方式の妥当性判断）に耐える経験が、実際にアサインされる人物にあるかを確認する。守り／攻めで技術的責任者が分かれているかも、体制の実効性を測る重要な情報。</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>良: 具体的な氏名・実例（社名または特定可能な粒度・連携方式・規模）を即答し、守り／攻めの技術責任者が明確に分かれている、または一人で両方に精通している理由を説明できる。
+危: 「チーム全体で対応します」（技術的責任者が不特定）。名前は出るが実例が抽象的（「システム導入の経験があります」で連携方式・規模の言及なし）。</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>その方は本件に何%稼働しますか。アドバイザーとしての助言的関与か、要件定義書・機能要件定義書の執筆に実働で入るか、明確にしてください。</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>技術的な責任者が明確でないなら、貴社の証跡ワークフロー・API連携の機能要件は誰が技術的な正しさを検証するのですか。その方が実働で入らない場合、要件定義の技術的な誤り（ベンダーが実装不可能な要件を書いてしまう等）は誰が防ぎますか。</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>A社: ライズ・コンサルティングへの個別質問</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>PMは田村様・豊田様のどちらですか。この場で確定してください。そのうえで、確定したPMご本人に伺います。難所③（ロジック実装）について、当社のExcelマクロ・R言語資産を「残す／移植する／作り直す」にどう仕分けるか、ご自身の言葉で進め方を説明してください。</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>「or」表記の解消と、実際に手を動かす人の実力の直接確認。資料の出来ではなく本人の頭で答えられるか。</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>良: PMを即確定し、本人が仕分け基準（再現性・保証要件・変更頻度等）を具体的に語る。
 危: 「受注後に最適な者を」と確定を避ける。本人が答えられず同席者が代弁する。</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>その仕分けで「作り直す」と判定されたロジックは、誰が・どのフェーズで作り直すのですか。本フェーズの成果物（機能要件）にはどの粒度で反映されますか。</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>確定できないなら、契約書に「PM候補2名のうち当社が指名できる」と記載できますか。あわせて両名の直近3ヶ月の他案件稼働状況を開示してください。</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr"/>
-      <c r="J14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>定価3,520万円から32%の値引きの原資は何ですか（稼働を削るのか、単価を下げるのか、投資と割り切るのか）。値引き後単価は設計フェーズ以降も維持されますか。ランク別単価×人数×稼働率×期間の内訳を提出してください。</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>採点ルール上の「極端な安値の実態確認」。入口価格で次フェーズから単価を戻すモデルなら総コストで逆転する。</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>良: 内訳を開示し、次フェーズ単価も数字で明言。
 危: 次フェーズ単価の明言を避ける。「戦略的価格です」のみで内訳非開示。</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>次フェーズ（設計・開発PMO）の想定単価表を提示してください。この単価で、御社の品質管理（AP層のレビュー工数）は週何時間確保されますか。</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>値引き前提の稼働計画で要件定義が難航（工数超過）した場合、真っ先に削られるのはどの作業ですか。品質管理・レビュー工数を削らないことを、どう保証しますか。</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr"/>
-      <c r="J15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr"/>
+      <c r="J16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>SSBJ／第三者保証／非財務データ基盤の類似案件について、会社としての実績を「社名・時期・御社の役割・定量成果」の4点セットで3件、提出してください。守秘義務で社名が出せない場合は、業種・売上規模・拠点数で特定可能な粒度まで。</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>個人経歴頼みの実績を「会社の能力」として検証する。3件出せなければQ5素点2を確定。</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>良: 4点セットで3件、役割が主体的（PMO・要件定義リード）。
 危: 個人の過去所属時代の実績を会社実績のように語る。役割が「支援・参画」のみ。</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>その3件のうち、想定通りに行かなかった点（失敗）と、本件に持ち込む回避策を各1つずつ教えてください。</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>会社実績が乏しい場合、SSBJ基準の解釈（例: 産業横断指標・セーフハーバーの扱い）は誰の知見で担保しますか。外部専門家を使うなら、その費用は見積りに含まれていますか。</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>「条件付き要件」を含むRFPに対して、ベンダーは通常リスクバッファを乗せるか「個別見積り」で回答してきます。条件付き要件を含むRFPで、実際にベンダーから比較可能な固定見積りを取れた事例はありますか。取れなかった場合、当社のベンダー選定は何を基準に行うことになりますか。</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>提案の中核方法論のアウトカム検証。「RFPは書けるがベンダーが値付けできない」なら本末転倒。</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>良: 事例があり、変動幅×段階見積り（ベース＋オプション）等の具体的な工夫を語れる。
 危: 「ベンダーと調整します」。事例なし＋対策も一般論。</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>条件付き要件の「変動幅」は誰がどう見積るのですか。変動幅ごとの段階見積りを求めるRFPフォーマットのサンプル（マスキング可）を提示できますか。</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>事例がないなら、ベンダーが高値バッファを乗せるリスクをどう抑えますか。RFP発出前のベンダー事前サウンディングを実施しますか。実施する場合、誰の工数で・本見積りに含まれていますか。</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr"/>
+      <c r="J18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>A5</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>御社成果物（要件定義書3点＋RFP本紙＋評価要領）と当社想定成果物10点の対応表を提出してください。特に「海外拠点拡張ロードマップ」「グローバルデータ収集要件書」はどの成果物のどの章で担保されますか。</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>成果物カバレッジの検証。「4文書に集約」の裏で当社要求が薄まっていないか。</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>良: 10点すべてに章レベルの対応があり、粒度差も自己申告。
 危: 対応表が「概ね含まれます」レベルで章の特定がない。</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>対応表で「一部含む」となる成果物について、当社想定粒度との差分を埋める場合の追加工数・費用を提示してください。</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>海外拠点拡張ロードマップが成果物にないのは「スコープ外」という理解でよいですか。含める場合の金額・期間影響を提示してください。</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr"/>
-      <c r="J18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19" ht="150" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>★A6</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Q4/C4</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>貴提案の攻めは「可視化・活用の初期仮説」までで、PBR向上・受注拡大への定量接続が見えません。CFP即応・削減貢献量といった当社の攻めユースケースを、要件定義期間中に「どの部門から・何のデータを取り・どの成果物に・どんな要件として」確定させるのか、進め方を具体的に説明してください。</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>書面でQ4素点3（一般論止まり）のA社に挽回機会を与え、攻め能力の実体を確認する。3社の攻めを同じ土俵で比較するための質問。</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>良: 当社の事業構造（Cat11・製品別原単位等）を踏まえ、ヒアリング先・必要データ・成果物への落とし込みを具体的に語れる。
 危: 「貴社と議論しながら決めます」（進め方の設計がない＝攻めは他社材料の後追い）。</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>削減貢献量（Scope4）は算定基準が確立していません。前提条件と算定方法の妥当性を、社外（投資家・顧客）にどう説明可能な形で要件化しますか。</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>攻めの要件化経験が乏しいなら、本件では守り（開示・保証）に集中し、攻めは初期仮説の提示までと割り切る提案と理解してよいですか。その場合の見積り減額余地はありますか。</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20" ht="150" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21" ht="150" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>★A7</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>宿題+即答</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>C1/D2</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>貴社の成果物一覧（業務・機能・非機能要件定義書＋RFP本紙）を照合したところ、独立したシステム構成図（アーキテクチャ）、独立したデータ要件定義書、ユースケースの優先順位付け（効果×実現性評価）が明示されていません。①これらは非機能要件定義書等に含まれる想定ですか、それとも本提案のスコープ外ですか。②スコープ外の場合、追加した場合の金額・期間影響を提示してください。</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>貴社の安さ（2,400万円）の一部は正当なスコープの狭さで説明できるはずだが、それを定量化する。安さが「効率」か「手抜き」かをこの回答で判別する。</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>良: 現在の成果物のどこに何が含まれるかを明確に切り分け、不足分の追加金額を具体的に提示。
 危: 「含まれています」と主張するが、成果物一覧のどの記載か特定できない。</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>アーキテクチャ図がないままRFPを発行した場合、ベンダー各社の提案アーキテクチャが比較できず、評価が長期化するリスクがあります。このリスクをどう考えますか。</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>含まれていないなら、貴社の2,400万円はPwC社の27,000,000円やアビーム社の基本スコープと同じ土俵で比較できません。追加金額を示せないなら、当社は貴社の見積りをそのままでは採用できません。</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="10" t="inlineStr"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22" ht="150" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>★A8</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Q3/Q4/Q6</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>参画予定メンバー（田村様・豊田様・中村様・渡辺様）のご経歴を確認したところ、いずれもPMO・企画構想・調査検証・GX戦略が中心で、システム連携（API／CSV連携方式の決定、既存システムとの接続要件定義）を主導した実務経験が経歴上明記されていません。本件のシステム構成・連携要件は、どなたが技術的に検証しますか。</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Q3（守り）の証跡・統制の機能要件化、Q4のシステム連携要件は、PMO経験だけでは技術的な妥当性を保証できない。本件で技術的に手を動かす／検証する人物が体制表のどこにいるのかを名指しで確認する。</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>良: 体制表にない技術担当（協力会社・専門家の起用）を明示するか、田村様等の経歴のうちシステム連携に該当する具体的な実務（IT・PMOの案件で連携方式まで決定した経験）を補足できる。
+危: 「チームとして総合的に対応します」（技術的な検証者が不特定のまま）。</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>技術担当を外部から起用する場合、その方の費用は2,400万円の見積りに含まれていますか、別途発生しますか。</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>技術的検証者がいないなら、貴社が作成するシステム構成方針・API等の連携要件（成果物一覧の「システム構成方針、アーキテクチャ、クラウド利用方針」）は、誰が実装可能性を保証するのですか。実装不可能な要件をRFPに書いてしまうリスクをどう防ぎますか。</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>B社: PwCコンサルティングへの個別質問</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="150" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>宿題+即答</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>100%稼働の実働3名（SA/A）の実名・経歴・類似案件経験を提示してください。提示できない場合、御社の品質保証は「SM20%のレビュー」に依存することになりますが、ジュニア3名の成果物をレビュー20%で品質担保できた同型案件の実例を示してください。</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>書面最大の弱点。実名が出ないなら「誰が来るか分からない提案」としてQ6素点2を確定させる。</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>良: 3名の実名・経歴・類似経験を提示。
 危: 「受注後にベストな人材を」＝アサイン未確定の証左。実例なしで「品質プロセスがあるので大丈夫」。</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>（実名が出た場合）3名の直近案件と本件との類似性、11月末までの他案件重複を開示してください。1名でも交代する場合の事前通知と当社承認プロセスを契約に入れられますか。</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>実名が出せないのは社内でアサインが確定していないからですか。それは受注後「集められる人で始める」ことを意味しませんか。キックオフ時点で確定している保証（確約書等）を出せますか。</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-    </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25" ht="150" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>D1/D2</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>線表はRFP発出12月末（仮）ですが、当社の要求は11月末です。前倒しは可能ですか。可能なら「何を削るか・体制をどう変えるか・金額はいくら変わるか」。不可能なら、その1ヶ月遅れが後続のベンダー選定〜2028年1月本番収集の逆線表にどう影響するか、御社の見解を示してください。</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>要求期限とのズレの認識確認。根拠なき「できます」も、理由曖昧な「できません」も減点。</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>良: 前倒し案が具体的（削るタスク・増員・金額差）か、12月末で間に合う逆線表を数字で示す。
 危: 「頑張ります」。逆線表なしの「問題ありません」。</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>前倒しのために削る作業は、後続フェーズのどこで・誰が・いくらで実施することになりますか（先送りの総コストを提示してください）。</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>12月末発出だと、ベンダーの提案期間が年末年始を挟みます。提案品質・参加意欲への影響と、当社の評価・稟議期間を含めて2028年1月に間に合う根拠を、週単位の逆線表で示してください。</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26" ht="150" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Q4/中立性</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>御社はNet Zero Cloud Partner of the Yearであり、自社アセット（PwC Net Zeroアセット）もお持ちです。本件RFPの評価軸設計において、Salesforce系ソリューションが構造的に有利になるバイアスをどう排除しますか。過去のツール選定支援で、御社の導入実績がないツールが選定された事例はありますか。</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>RFP作成者のバイアスは要件の書き方に必ず現れる。実例で中立性を証明できるか。</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>良: 実例＋プロセス上の仕掛け（評価軸の貴社承認、製品非依存の要件記述等）。
 危: 「中立に評価します」の宣言のみ。実例なし。</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>評価軸の設計に、当社＋第三者（御社と利害関係のない専門家）のレビューを入れることに同意しますか。PwC Net Zeroアセットを本件の候補から除外することは可能ですか。</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>導入実績のないツールが選ばれた事例がないなら、それは御社のRFPが実績あるツールに最適化されている証左ではありませんか。機能要件を製品非依存で記述する具体的な方法（記述例）を示してください。</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27" ht="150" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>C3/Q2</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>御社提案は「ルール策定・算定ロジックは当社にて策定済み」を前提としています。要件定義開始後にこの前提が崩れていた（未策定・不十分と判明した）場合、追加費用と期間影響はどうなりますか。契約前に条件を明文化できますか。</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>最も楽観的な前提を置いた提案。変更管理の実運用を契約条件レベルで確定させる。</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>良: 前提検証の方法と、崩れた場合の費用・期間の扱いを具体的に提示。
 危: 「その際はご相談」のみで基準なし。</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>最初の2週間のAs-Is確認で前提を検証するチェックリストを提示できますか。「策定済み」と判定する基準を契約前に当社と合意しましょう。</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>再見積りとなる場合の適用単価と、期間延長時の11月末（当社要求）への影響を試算してください。前提リスクを織り込んだ固定価格案を提示できますか。</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26" ht="150" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28" ht="150" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>将来予測・Scope3一次データ化をStep2以降とされていますが、今回のRFPに拡張性要件として織り込まなければ、Step2で基盤の作り直しが発生しませんか。Step2を見据えて今回のRFPに最低限入れるべき要件を、この場で3つ挙げてください。</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>「後ろ倒し」の設計思想が手戻りリスクを内包していないかの検証。</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>良: データモデル・API・マスタ構造など基盤側に効く拡張性要件を即答。
 危: 「Step2で改めて検討」（＝作り直し容認）。</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>その3つの要件はRFPでMust要件にしますか、評価加点にしますか。Must化した場合の初期構築コストへの影響見立てを教えてください。</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>Step2で基盤を作り直した事例・作り直さずに済んだ事例を各1つ挙げ、何が分かれ目だったかを説明してください。</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27" ht="150" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>★B6</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>御見積書の案②（27,000,000円）には「1-4 業務要件定義書作成」1タスクのみが業務要件側の記載ですが、当社が別途照合したところ、機能要件定義書・データ要件定義書・システム要件定義書に相当する独立した記載が価格表上で確認できません。①これらは1-4に含まれますか、②含まれないなら追加のタスク・金額が必要ですか、を明確にしてください。</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>27,000,000円が3社中最も割安に見えるが、実は機能/データ/システム要件の独立文書化が価格表に見えないだけかもしれない。曖昧なまま比較すると不当にPwCを過大評価するリスクがあるため、この場で解消する。</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>良: 1-4の範囲を明確に定義し、含まれる場合はその粒度（アビームの#6〜#8相当か）を具体的に示す。含まれない場合は金額を明示。
 危: 「業務要件定義書に含まれます」で粒度の説明がない。</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>機能要件定義書を独立文書として発行することは可能ですか。その場合、貴社の成果物マッピング表（P.40）に記載の「システム機能要求一覧」等との対応関係を教えてください。</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>含まれないなら、案②の27,000,000円は当社が想定する成果物10点を満たしていない可能性があります。満たすための追加金額を今この場で概算で示してください。</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30" ht="150" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>★B7</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Q3/Q4/Q6</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>アドバイザーの小泉様は、システム開発の要件定義・設計・開発・テスト・展開の各工程に精通し、複数システムを跨いだアーキテクチャ構想の実績をお持ちと理解しています。この方は本件に何%稼働されますか。100%稼働の実働3名（SA/A、TBD）とは別枠のアドバイザーとしての関与ですか、それともアーキテクチャ検討フェーズ（2-1）に実働で入っていただけますか。</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>貴社の体制で最もシステム連携・アーキテクチャの実務経験が濃い人物が、実は5%関与のアドバイザー層に位置づけられている可能性がある。技術的に最も適した人材が実働に入らないなら、実働3名（TBD）でアーキテクチャ素案の品質を担保できるかが疑わしい。</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>良: 小泉様がアーキテクチャ検討フェーズに実働で一定時間入る、または実働3名のうち1名が小泉様と同等の経験を持つことを具体的に説明。
+危: 「アドバイザーとして必要時にレビューします」（実働に入らないことを言い換えているだけ）。</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>実働3名（TBD）のうち、システム連携・アーキテクチャ設計を担当する予定の方の想定経歴（役職・経験年数・類似実績の有無）を教えてください。</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>小泉様が実働に入らず、実働3名もTBDのままだと、アーキテクチャ素案（2-1）の技術的な妥当性は誰が保証するのですか。品質管理責任者（須貝様、20%関与）のレビューだけで十分と言える根拠を示してください。</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>C社: アビームコンサルティングへの個別質問</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="150" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="150" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>【v1.1反映】基本スコープ5,300万円（オプションA/B分離済み）について、ランク別単価×人数×稼働率×期間の内訳を提出してください。あわせて、基本スコープの各タスク（#1〜#10、#12の一部）と内訳の対応表を示し、どのタスクに最も工数を要しているかを明示してください。</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>分離自体は完了済みだが、なお5,300万円が他社の1.6〜2.2倍である原因が「単価水準」か「投入人数・稼働率」かは、この内訳でしか切り分けられない。</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>良: 内訳つきで提出し、単価が他社と同水準（品質差で説明できる）か、単価自体が高い（品質と無関係な割高要因）かが判別できる。
 危: 総額のみで内訳を示さない、又はタスク対応が粗い。</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>最も工数を要するタスクはどれですか。そのタスクが期間内に完了しなかった場合、どのタスクの工数を削って吸収しますか。</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>内訳が出せない理由は何ですか。準委任契約で工数内訳が開示できないのは説明がつきません。開示なしで5,300万円の妥当性を当社はどう検証すればよいのですか。</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30" ht="150" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33" ht="150" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>RFP発行「年内」を11月末に前倒しできますか。ボトルネックは何ですか。前倒しのために当社が9月中に意思決定すべき事項を、優先順位付きで挙げてください。</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>2028/1逆算を掲げる同社が「12月で間に合う」と考えるなら、その根拠を数字で語らせる。合理的なら当社計画の見直し材料にもなる。</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>良: 前倒しの条件（当社の意思決定期限・削る要素）を具体的に提示、または12月案の合理性を逆線表で証明。
 危: 「調整可能です」のみ。ボトルネックを特定できない。</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>11月末発行の前倒し案において、当社が9月中に決められなかった場合の縮退ルール（どの要件を条件付きに落とすか）を事前合意できますか。</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>「12月で間に合う」根拠の逆線表で、ベンダー評価が1月末に完了しなかった場合（回答遅延・再質疑）のバッファはどこにありますか。2027年中構築完了のクリティカルパスには何日の余裕がありますか。</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr"/>
-      <c r="J30" s="10" t="inlineStr"/>
-    </row>
-    <row r="31" ht="150" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34" ht="150" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>中立性</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>御社はベンダー評価・選定までをスコープに含め、ソリューションベンダーとのリレーションを強みとして挙げています。後続の導入フェーズを御社自身が受注する意思はありますか。ある場合、要件定義・RFP・評価軸が御社の得意なソリューションや自社導入体制に有利に働かないことをどう担保しますか。</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>「RFPを書く者が選定も行い、導入も狙う」構造は最も利益相反が起きやすい。導入受注の意思を先に言質として取る。</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t>良: 受注意思の有無を明言し、ある場合は評価から自社を外す設計に同意。
 危: 「その時点で検討」（意思を曖昧にしたまま選定に関与し続ける）。</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>導入を受注しないと明言できるなら、それを契約書（入札制限条項）に明記できますか。受注可能性を残すなら、ベンダー評価プロセスから御社を外し「当社＋第三者評価」とする設計に同意しますか。</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>「中立評価」の実績として、御社リレーション外のベンダーが選定された割合を開示してください。RFP発出先リストの選定基準は誰が作り、誰が承認しますか。</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32" ht="150" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr"/>
+      <c r="J34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35" ht="150" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>「参画メンバーは変更になる可能性があります」の注記を撤回し、主要5名（豊嶋・山野・平野・張本・今野の各氏）の稼働率%・期間中の交代禁止（または交代時の品質担保条件）を確約できますか。また、SGホールディングス案件等、同時期に走る大型案件との要員重複はありませんか。</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>実名の豪華さと実際の稼働は別物。特にプリンシパル・ダイレクター級の実稼働%を数字で確定させる。</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>良: 月別稼働率%と交代条件を書面で確約。重複を正直に開示。
 危: 注記を維持したまま「基本的には変わりません」。アドバイザーの稼働が「適宜」のまま。</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>プリンシパル・ダイレクター級は実質週何時間を本件に使いますか。定例会議出席以外の実働（成果物レビュー時間）をコミットできますか。</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>注記を撤回できない理由は何ですか。交代時に「同等以上のランク・類似経験者を当社承認のうえ配置」する条項を契約に入れられますか。</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33" ht="150" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36" ht="150" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>C4/Q4</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>「工数削減額・リスク回避額・収益機会」の効果3分類について、過去案件で経営会議が実際に投資承認した試算の実例を1件、数字の粒度が分かる形で紹介してください（社名は伏せて構いません）。「CFP即応が受注シェアに直結」という仮説の根拠となるデータはありますか。</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>攻めのストーリーが「営業トーク」か「再現可能な方法論」かの見極め。</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>良: 実例の試算構造（前提・データソース・金額規模）を具体的に説明。
 危: フレームワークの説明に終始し実例が出ない。</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>その実例の試算ロジックを本件に適用した場合、当社のROI試算はいつ時点で・どの精度で出せますか。当社の経営上申（投資承認）のタイミングとどう整合させますか。</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>実例が出せないなら、効果3分類は概念に留まります。数億円規模になる基盤構築の投資判断を支える定量根拠を、この要件定義期間中に・どのデータで作るのか説明してください。</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr"/>
-      <c r="J33" s="10" t="inlineStr"/>
-    </row>
-    <row r="34" ht="150" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr"/>
+      <c r="J36" s="10" t="inlineStr"/>
+    </row>
+    <row r="37" ht="150" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>★C6</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Q2/Q5</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>「戦略依存×Must/Should/Could」の4象限と二層整理（共通要件＋テーマ別シナリオ）を適用した過去案件で、①線引きの判断が貴社とクライアントで割れた実例と収拾方法、②戦略確定後に実際にRFP要件がどれだけ変わったか（変更件数・変更率）を教えてください。</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>書面で最高評価（Q2素点5）をつけた中核方法論の実効性検証。素点5は「裏付け完全」が要件のため、高得点ほど質疑での検証が必須。方法論が本当に手戻りを減らしたのかをアウトカム（変更率）で証明させる。</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>良: 割れた実例を率直に語り、変更率を数字で示せる（例: 戦略確定後の要件変更が全体の○%に収まり、うち構造変更はゼロ等）。
 危: 「うまくいきました」のみで数字なし。割れた実例が「ない」（適用実績が浅いか、都合の悪い情報を出さない）。</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>本件でMust×戦略非依存の「骨格」に置くと仰る組織マスタ・証憑統制・Scope1/2算定のうち、実は当社の戦略次第で動き得るものはどれですか。骨格の線引きを最初の何週で当社と合意しますか。</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>変更率のデータがないなら、「手戻り最小化」の効果は測定されていない主張になります。本件では何をもって「手戻りが最小化された」と評価すればよいか、測定可能な形で定義してください。</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr"/>
-      <c r="J34" s="10" t="inlineStr"/>
-    </row>
-    <row r="35" ht="150" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38" ht="150" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>★C7</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>当社にて成果物を照合したところ、PwC社の27,000,000円の見積り（3.6ヶ月）には「開示効率化検討」「展開計画・定着計画」「PJ計画書」が含まれていますが、貴社の基本スコープ5,300万円（3.9ヶ月）にはこれらが含まれず、オプションBに切り出されています。つまり貴社の基本スコープは他社より成果物が狭いにもかかわらず、価格はPwC社の約2倍です。この差の主因は単価水準ですか、投入人数ですか。ランク別内訳（C1の宿題回答）でご説明ください。</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>最も鋭い一問。品質でもスコープでも説明のつかない価格差（超過コスト）を、貴社自身に他社比較で直接答えさせる。回避不能な形で単価水準の説明責任を負わせる。</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>良: 単価が他社より高い理由を明確に説明（シニアリティ、専門性、リスクプレミアム等）し、その根拠を具体的な数字・実例で示す。
 危: 「価値が違います」等の定性論で数字を出さない。他社見積りの前提を問題にして自社の説明を回避する。</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>その単価差に見合う成果（例: 手戻りゼロ、保証人指摘ゼロ）を過去案件で実現した実例はありますか。本件でその成果を測定可能な形で契約に落とし込めますか。</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>説明できないなら、貴社の基本スコープ価格は市場価格から外れている可能性があります。PwC社の27,000,000円の内容に貴社の強み（2段階アーキテクチャ・独立データ要件定義書）を追加した場合の増分見積りを、この場で概算で示してください。</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr"/>
-      <c r="J35" s="10" t="inlineStr"/>
+      <c r="I38" s="10" t="inlineStr"/>
+      <c r="J38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39" ht="150" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>★C8</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Q3/Q4/Q6</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>アドバイザーの森銅様は、SSBJ対応向けシステム要件定義・導入実績（物流業・化学メーカー・非鉄金属メーカー等）を複数お持ちと理解しています。この方の本件での実稼働率は体制表で「適宜」とありますが、具体的に週何時間、基本スコープのどのタスク（#4システム構成案策定・#8システム要件定義等）を担当されますか。また、攻め側（#2出口設計のユースケース優先順位付け）を主導するのはどなたですか、その方の類似実績を教えてください。</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>貴社の体制で最もシステム連携・SSBJシステム導入の実務経験が濃い人物（森銅様）が「適宜」という低稼働の位置づけになっている。守り担当（森銅様）と攻め担当が明確に分かれているか、それぞれの実働時間を具体的に確認する。</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>良: 森銅様の週次稼働時間とタスク対応を具体的に提示し、攻め担当者（別人物）の実例も明示。
+危: 「必要に応じて随時サポートします」（稼働時間・タスク対応が不明確）。</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>森銅様が「適宜」ではなく特定タスク（#4・#8等）に固定的にコミットする形に変更できますか。その場合の稼働率%と体制表の更新版を提出してください。</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>「適宜」のままだと、基本スコープの技術的な品質は山野様（マネージャー）と平野様（シニアコンサルタント）と貴社選定のコンサルタント3名（人数調整）に依存することになります。この体制でシステム構成案（#4）の技術的妥当性を担保できる根拠を示してください。</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr"/>
+      <c r="J39" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A13:J13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/コンペ質疑_質問票.xlsx
+++ b/docs/コンペ質疑_質問票.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検（第1回）で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。⑦アビームv1.1改訂（基本/オプション分離）と成果物カバレッジ照合（第2回再点検）を反映しC1・★A7・★B6・★C7を追加/更新。スコープ差は双方向（アビームが広い部分／PwC案②が広い部分の両方が存在）のため、価格差を単純にスコープや品質だけで説明させない設計。⑧第3回再点検: アサインメンバーの経歴を「攻め／守り」の技術専門性（システム連携・API連携経験等）で照合し、★共8・★A8・★B7・★C8を追加。Q6は実名・経歴の有無までしか採点していないため、本件の技術判断に耐える経験の有無と、その人物が実働で入るか（アドバイザー止まりでないか）を別途確認する。</t>
+          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検（第1回）で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。⑦アビームv1.1改訂（基本/オプション分離）と成果物カバレッジ照合（第2回再点検）を反映しC1・★A7・★B6・★C7を追加/更新。スコープ差は双方向（アビームが広い部分／PwC案②が広い部分の両方が存在）のため、価格差を単純にスコープや品質だけで説明させない設計。⑧第3回再点検: アサインメンバーの経歴を「攻め／守り」の技術専門性（システム連携・API連携経験等）で照合し、★共8・★A8・★B7・★C8を追加。Q6は実名・経歴の有無までしか採点していないため、本件の技術判断に耐える経験の有無と、その人物が実働で入るか（アドバイザー止まりでないか）を別途確認する。⑨第4回再点検: 5つの難所（貴社RFP由来の共通言語）×深さレベル（L0前提化〜L4詳細設計）×担当で3社を独立照合した結果を踏まえ、★共9（自己採点による照合）・★A9（ライズの深さの天井を即答で検証）・★B8（PwCの前提化・後ろ倒しが戦略判断か能力の限界か）・★C9（アビーム提案書内の難所①に関する記述矛盾の解消）を追加。</t>
         </is>
       </c>
     </row>
@@ -1031,1097 +1031,1277 @@
       <c r="I13" s="10" t="inlineStr"/>
       <c r="J13" s="10" t="inlineStr"/>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>★共9</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>宿題+即答</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Q1/Q2/Q3/Q4</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>当社は貴社提案を「5つの難所」それぞれについて、深さレベル（L0=前提として扱う／L1=初期仮説の提示のみ／L2=検討方法論の提示／L3=具体的な設計・詳細ルールの確定／L4=詳細設計・物理設計まで）で独自に照合しました。この同じ物差しで、貴社ご自身の提案内容を難所①〜⑤それぞれについて自己採点してください。当社の照合結果と異なる場合は、提案書のどの記載を根拠にその深さと判断したか、具体的に指し示してください。</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>発注者側の物差しを提示し自己採点させることで、①提案書の記載を実際より深く見せる表現（スピン）の有無、②各社が自社の弱点（前提化・後ろ倒しにした難所）を正直に認識しているかを検証する。自己採点と当社の独立照合のズレそのものが評価材料になる。</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>良: 当社の照合結果とほぼ一致、または一致しない箇所について提案書の具体的な記載箇所を示して合理的に反論できる。
+危: 全難所をL3〜L4と高く自己採点する（スピンの兆候）。自己採点を曖昧にする・拒む。</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>自己採点がL1〜L2の難所について、次工程（設計フェーズ）でどこまで深さを引き上げる計画ですか。その工程・期間を教えてください。</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>当社の照合では、貴社の弱い難所はL0〜L1相当と評価しています。貴社の自己採点がこれと異なるなら、その根拠となる提案書の記載箇所（ページ）を今この場で指し示してください。指し示せないなら、当社の評価が正確ということで確定します。</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>A社: ライズ・コンサルティングへの個別質問</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>PMは田村様・豊田様のどちらですか。この場で確定してください。そのうえで、確定したPMご本人に伺います。難所③（ロジック実装）について、当社のExcelマクロ・R言語資産を「残す／移植する／作り直す」にどう仕分けるか、ご自身の言葉で進め方を説明してください。</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>「or」表記の解消と、実際に手を動かす人の実力の直接確認。資料の出来ではなく本人の頭で答えられるか。</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>良: PMを即確定し、本人が仕分け基準（再現性・保証要件・変更頻度等）を具体的に語る。
 危: 「受注後に最適な者を」と確定を避ける。本人が答えられず同席者が代弁する。</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>その仕分けで「作り直す」と判定されたロジックは、誰が・どのフェーズで作り直すのですか。本フェーズの成果物（機能要件）にはどの粒度で反映されますか。</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>確定できないなら、契約書に「PM候補2名のうち当社が指名できる」と記載できますか。あわせて両名の直近3ヶ月の他案件稼働状況を開示してください。</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr"/>
-      <c r="J15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr"/>
+      <c r="J16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>定価3,520万円から32%の値引きの原資は何ですか（稼働を削るのか、単価を下げるのか、投資と割り切るのか）。値引き後単価は設計フェーズ以降も維持されますか。ランク別単価×人数×稼働率×期間の内訳を提出してください。</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>採点ルール上の「極端な安値の実態確認」。入口価格で次フェーズから単価を戻すモデルなら総コストで逆転する。</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>良: 内訳を開示し、次フェーズ単価も数字で明言。
 危: 次フェーズ単価の明言を避ける。「戦略的価格です」のみで内訳非開示。</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>次フェーズ（設計・開発PMO）の想定単価表を提示してください。この単価で、御社の品質管理（AP層のレビュー工数）は週何時間確保されますか。</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>値引き前提の稼働計画で要件定義が難航（工数超過）した場合、真っ先に削られるのはどの作業ですか。品質管理・レビュー工数を削らないことを、どう保証しますか。</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>SSBJ／第三者保証／非財務データ基盤の類似案件について、会社としての実績を「社名・時期・御社の役割・定量成果」の4点セットで3件、提出してください。守秘義務で社名が出せない場合は、業種・売上規模・拠点数で特定可能な粒度まで。</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>個人経歴頼みの実績を「会社の能力」として検証する。3件出せなければQ5素点2を確定。</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>良: 4点セットで3件、役割が主体的（PMO・要件定義リード）。
 危: 個人の過去所属時代の実績を会社実績のように語る。役割が「支援・参画」のみ。</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>その3件のうち、想定通りに行かなかった点（失敗）と、本件に持ち込む回避策を各1つずつ教えてください。</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>会社実績が乏しい場合、SSBJ基準の解釈（例: 産業横断指標・セーフハーバーの扱い）は誰の知見で担保しますか。外部専門家を使うなら、その費用は見積りに含まれていますか。</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr"/>
+      <c r="J18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>「条件付き要件」を含むRFPに対して、ベンダーは通常リスクバッファを乗せるか「個別見積り」で回答してきます。条件付き要件を含むRFPで、実際にベンダーから比較可能な固定見積りを取れた事例はありますか。取れなかった場合、当社のベンダー選定は何を基準に行うことになりますか。</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>提案の中核方法論のアウトカム検証。「RFPは書けるがベンダーが値付けできない」なら本末転倒。</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>良: 事例があり、変動幅×段階見積り（ベース＋オプション）等の具体的な工夫を語れる。
 危: 「ベンダーと調整します」。事例なし＋対策も一般論。</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>条件付き要件の「変動幅」は誰がどう見積るのですか。変動幅ごとの段階見積りを求めるRFPフォーマットのサンプル（マスキング可）を提示できますか。</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>事例がないなら、ベンダーが高値バッファを乗せるリスクをどう抑えますか。RFP発出前のベンダー事前サウンディングを実施しますか。実施する場合、誰の工数で・本見積りに含まれていますか。</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr"/>
-      <c r="J18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19" ht="150" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>A5</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>御社成果物（要件定義書3点＋RFP本紙＋評価要領）と当社想定成果物10点の対応表を提出してください。特に「海外拠点拡張ロードマップ」「グローバルデータ収集要件書」はどの成果物のどの章で担保されますか。</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>成果物カバレッジの検証。「4文書に集約」の裏で当社要求が薄まっていないか。</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>良: 10点すべてに章レベルの対応があり、粒度差も自己申告。
 危: 対応表が「概ね含まれます」レベルで章の特定がない。</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>対応表で「一部含む」となる成果物について、当社想定粒度との差分を埋める場合の追加工数・費用を提示してください。</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>海外拠点拡張ロードマップが成果物にないのは「スコープ外」という理解でよいですか。含める場合の金額・期間影響を提示してください。</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20" ht="150" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21" ht="150" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>★A6</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Q4/C4</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>貴提案の攻めは「可視化・活用の初期仮説」までで、PBR向上・受注拡大への定量接続が見えません。CFP即応・削減貢献量といった当社の攻めユースケースを、要件定義期間中に「どの部門から・何のデータを取り・どの成果物に・どんな要件として」確定させるのか、進め方を具体的に説明してください。</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>書面でQ4素点3（一般論止まり）のA社に挽回機会を与え、攻め能力の実体を確認する。3社の攻めを同じ土俵で比較するための質問。</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>良: 当社の事業構造（Cat11・製品別原単位等）を踏まえ、ヒアリング先・必要データ・成果物への落とし込みを具体的に語れる。
 危: 「貴社と議論しながら決めます」（進め方の設計がない＝攻めは他社材料の後追い）。</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>削減貢献量（Scope4）は算定基準が確立していません。前提条件と算定方法の妥当性を、社外（投資家・顧客）にどう説明可能な形で要件化しますか。</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>攻めの要件化経験が乏しいなら、本件では守り（開示・保証）に集中し、攻めは初期仮説の提示までと割り切る提案と理解してよいですか。その場合の見積り減額余地はありますか。</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="10" t="inlineStr"/>
-    </row>
-    <row r="21" ht="150" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22" ht="150" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>★A7</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>宿題+即答</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>C1/D2</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>貴社の成果物一覧（業務・機能・非機能要件定義書＋RFP本紙）を照合したところ、独立したシステム構成図（アーキテクチャ）、独立したデータ要件定義書、ユースケースの優先順位付け（効果×実現性評価）が明示されていません。①これらは非機能要件定義書等に含まれる想定ですか、それとも本提案のスコープ外ですか。②スコープ外の場合、追加した場合の金額・期間影響を提示してください。</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>貴社の安さ（2,400万円）の一部は正当なスコープの狭さで説明できるはずだが、それを定量化する。安さが「効率」か「手抜き」かをこの回答で判別する。</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>良: 現在の成果物のどこに何が含まれるかを明確に切り分け、不足分の追加金額を具体的に提示。
 危: 「含まれています」と主張するが、成果物一覧のどの記載か特定できない。</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>アーキテクチャ図がないままRFPを発行した場合、ベンダー各社の提案アーキテクチャが比較できず、評価が長期化するリスクがあります。このリスクをどう考えますか。</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>含まれていないなら、貴社の2,400万円はPwC社の27,000,000円やアビーム社の基本スコープと同じ土俵で比較できません。追加金額を示せないなら、当社は貴社の見積りをそのままでは採用できません。</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22" ht="150" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>★A8</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Q3/Q4/Q6</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>参画予定メンバー（田村様・豊田様・中村様・渡辺様）のご経歴を確認したところ、いずれもPMO・企画構想・調査検証・GX戦略が中心で、システム連携（API／CSV連携方式の決定、既存システムとの接続要件定義）を主導した実務経験が経歴上明記されていません。本件のシステム構成・連携要件は、どなたが技術的に検証しますか。</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Q3（守り）の証跡・統制の機能要件化、Q4のシステム連携要件は、PMO経験だけでは技術的な妥当性を保証できない。本件で技術的に手を動かす／検証する人物が体制表のどこにいるのかを名指しで確認する。</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>良: 体制表にない技術担当（協力会社・専門家の起用）を明示するか、田村様等の経歴のうちシステム連携に該当する具体的な実務（IT・PMOの案件で連携方式まで決定した経験）を補足できる。
 危: 「チームとして総合的に対応します」（技術的な検証者が不特定のまま）。</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>技術担当を外部から起用する場合、その方の費用は2,400万円の見積りに含まれていますか、別途発生しますか。</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>技術的検証者がいないなら、貴社が作成するシステム構成方針・API等の連携要件（成果物一覧の「システム構成方針、アーキテクチャ、クラウド利用方針」）は、誰が実装可能性を保証するのですか。実装不可能な要件をRFPに書いてしまうリスクをどう防ぎますか。</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>★A9</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Q2/Q3</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>貴社の5つの難所への対応は、いずれも初期仮説の提示（当社評価でL1〜L2）に留まっています。一例として難所④（内部統制と承認フロー）について、この場で、統制要素×確認領域のマトリクスから責任所在・データ出所・完全性・妥当性の4軸で役割分担を設計する——という粒度まで、口頭で具体的に説明してください。</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>書面のL1〜L2が「現時点の実力の限界」か「意図的に抑えた記載」かを、この場で即答させることで判別する。具体的に語れれば実力はあるが記載を絞った可能性、語れなければ書面のL1〜L2が実力の天井である可能性が高い。</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>良: 統制要素と確認領域の切り分け、責任分担の考え方をこの場で具体的に語れる。
+危: 「それは設計フェーズで検討します」を繰り返す（具体化する実力が確認できない）。</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>（具体的に語れた場合）なぜ提案書にはこの具体度を記載しなかったのですか。書面と実力の間にギャップがあるなら、他の難所についても同様に確認させてください。</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>（語れない場合）難所④の統制設計は貴社にとって専門外の領域ということでよいですか。その場合、証跡管理・監査対応要件の機能要件化は、実際には誰が技術的に検証するのですか。</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>B社: PwCコンサルティングへの個別質問</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="150" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>宿題+即答</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>100%稼働の実働3名（SA/A）の実名・経歴・類似案件経験を提示してください。提示できない場合、御社の品質保証は「SM20%のレビュー」に依存することになりますが、ジュニア3名の成果物をレビュー20%で品質担保できた同型案件の実例を示してください。</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>書面最大の弱点。実名が出ないなら「誰が来るか分からない提案」としてQ6素点2を確定させる。</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>良: 3名の実名・経歴・類似経験を提示。
 危: 「受注後にベストな人材を」＝アサイン未確定の証左。実例なしで「品質プロセスがあるので大丈夫」。</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>（実名が出た場合）3名の直近案件と本件との類似性、11月末までの他案件重複を開示してください。1名でも交代する場合の事前通知と当社承認プロセスを契約に入れられますか。</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>実名が出せないのは社内でアサインが確定していないからですか。それは受注後「集められる人で始める」ことを意味しませんか。キックオフ時点で確定している保証（確約書等）を出せますか。</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27" ht="150" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>D1/D2</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>線表はRFP発出12月末（仮）ですが、当社の要求は11月末です。前倒しは可能ですか。可能なら「何を削るか・体制をどう変えるか・金額はいくら変わるか」。不可能なら、その1ヶ月遅れが後続のベンダー選定〜2028年1月本番収集の逆線表にどう影響するか、御社の見解を示してください。</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>要求期限とのズレの認識確認。根拠なき「できます」も、理由曖昧な「できません」も減点。</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>良: 前倒し案が具体的（削るタスク・増員・金額差）か、12月末で間に合う逆線表を数字で示す。
 危: 「頑張ります」。逆線表なしの「問題ありません」。</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>前倒しのために削る作業は、後続フェーズのどこで・誰が・いくらで実施することになりますか（先送りの総コストを提示してください）。</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>12月末発出だと、ベンダーの提案期間が年末年始を挟みます。提案品質・参加意欲への影響と、当社の評価・稟議期間を含めて2028年1月に間に合う根拠を、週単位の逆線表で示してください。</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26" ht="150" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28" ht="150" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Q4/中立性</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>御社はNet Zero Cloud Partner of the Yearであり、自社アセット（PwC Net Zeroアセット）もお持ちです。本件RFPの評価軸設計において、Salesforce系ソリューションが構造的に有利になるバイアスをどう排除しますか。過去のツール選定支援で、御社の導入実績がないツールが選定された事例はありますか。</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>RFP作成者のバイアスは要件の書き方に必ず現れる。実例で中立性を証明できるか。</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>良: 実例＋プロセス上の仕掛け（評価軸の貴社承認、製品非依存の要件記述等）。
 危: 「中立に評価します」の宣言のみ。実例なし。</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>評価軸の設計に、当社＋第三者（御社と利害関係のない専門家）のレビューを入れることに同意しますか。PwC Net Zeroアセットを本件の候補から除外することは可能ですか。</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>導入実績のないツールが選ばれた事例がないなら、それは御社のRFPが実績あるツールに最適化されている証左ではありませんか。機能要件を製品非依存で記述する具体的な方法（記述例）を示してください。</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27" ht="150" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>C3/Q2</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>御社提案は「ルール策定・算定ロジックは当社にて策定済み」を前提としています。要件定義開始後にこの前提が崩れていた（未策定・不十分と判明した）場合、追加費用と期間影響はどうなりますか。契約前に条件を明文化できますか。</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>最も楽観的な前提を置いた提案。変更管理の実運用を契約条件レベルで確定させる。</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>良: 前提検証の方法と、崩れた場合の費用・期間の扱いを具体的に提示。
 危: 「その際はご相談」のみで基準なし。</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>最初の2週間のAs-Is確認で前提を検証するチェックリストを提示できますか。「策定済み」と判定する基準を契約前に当社と合意しましょう。</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>再見積りとなる場合の適用単価と、期間延長時の11月末（当社要求）への影響を試算してください。前提リスクを織り込んだ固定価格案を提示できますか。</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28" ht="150" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30" ht="150" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>将来予測・Scope3一次データ化をStep2以降とされていますが、今回のRFPに拡張性要件として織り込まなければ、Step2で基盤の作り直しが発生しませんか。Step2を見据えて今回のRFPに最低限入れるべき要件を、この場で3つ挙げてください。</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>「後ろ倒し」の設計思想が手戻りリスクを内包していないかの検証。</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>良: データモデル・API・マスタ構造など基盤側に効く拡張性要件を即答。
 危: 「Step2で改めて検討」（＝作り直し容認）。</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>その3つの要件はRFPでMust要件にしますか、評価加点にしますか。Must化した場合の初期構築コストへの影響見立てを教えてください。</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>Step2で基盤を作り直した事例・作り直さずに済んだ事例を各1つ挙げ、何が分かれ目だったかを説明してください。</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr"/>
-      <c r="J28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29" ht="150" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31" ht="150" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>★B6</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>御見積書の案②（27,000,000円）には「1-4 業務要件定義書作成」1タスクのみが業務要件側の記載ですが、当社が別途照合したところ、機能要件定義書・データ要件定義書・システム要件定義書に相当する独立した記載が価格表上で確認できません。①これらは1-4に含まれますか、②含まれないなら追加のタスク・金額が必要ですか、を明確にしてください。</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>27,000,000円が3社中最も割安に見えるが、実は機能/データ/システム要件の独立文書化が価格表に見えないだけかもしれない。曖昧なまま比較すると不当にPwCを過大評価するリスクがあるため、この場で解消する。</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>良: 1-4の範囲を明確に定義し、含まれる場合はその粒度（アビームの#6〜#8相当か）を具体的に示す。含まれない場合は金額を明示。
 危: 「業務要件定義書に含まれます」で粒度の説明がない。</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>機能要件定義書を独立文書として発行することは可能ですか。その場合、貴社の成果物マッピング表（P.40）に記載の「システム機能要求一覧」等との対応関係を教えてください。</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>含まれないなら、案②の27,000,000円は当社が想定する成果物10点を満たしていない可能性があります。満たすための追加金額を今この場で概算で示してください。</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30" ht="150" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32" ht="150" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>★B7</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Q3/Q4/Q6</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>アドバイザーの小泉様は、システム開発の要件定義・設計・開発・テスト・展開の各工程に精通し、複数システムを跨いだアーキテクチャ構想の実績をお持ちと理解しています。この方は本件に何%稼働されますか。100%稼働の実働3名（SA/A、TBD）とは別枠のアドバイザーとしての関与ですか、それともアーキテクチャ検討フェーズ（2-1）に実働で入っていただけますか。</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>貴社の体制で最もシステム連携・アーキテクチャの実務経験が濃い人物が、実は5%関与のアドバイザー層に位置づけられている可能性がある。技術的に最も適した人材が実働に入らないなら、実働3名（TBD）でアーキテクチャ素案の品質を担保できるかが疑わしい。</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>良: 小泉様がアーキテクチャ検討フェーズに実働で一定時間入る、または実働3名のうち1名が小泉様と同等の経験を持つことを具体的に説明。
 危: 「アドバイザーとして必要時にレビューします」（実働に入らないことを言い換えているだけ）。</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>実働3名（TBD）のうち、システム連携・アーキテクチャ設計を担当する予定の方の想定経歴（役職・経験年数・類似実績の有無）を教えてください。</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>小泉様が実働に入らず、実働3名もTBDのままだと、アーキテクチャ素案（2-1）の技術的な妥当性は誰が保証するのですか。品質管理責任者（須貝様、20%関与）のレビューだけで十分と言える根拠を示してください。</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr"/>
-      <c r="J30" s="10" t="inlineStr"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33" ht="150" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>★B8</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Q1/Q4</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>貴社は難所①（ルール策定）を「事前にLION様にて策定済みと想定」、難所⑤（可視化・活用）を「Step2以降」と、いずれも本フェーズの検討対象から明示的に外しています。これは「今回のスコープでは扱わない方が良い」という貴社の戦略的判断ですか、それとも貴社の専門性の範囲外だからですか。当社が①⑤を本フェーズに含めたい場合、体制・見積りはどう変わりますか。</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>貴社の強み（②③の実務詳細設計）と弱み（①⑤の戦略・攻めへの関与）が、意図的なスコーピングか能力の限界かを判別する。意図的なら交渉で範囲を広げられる可能性があり、能力の限界なら体制強化や他社との組み合わせが必要になる。</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>良: 「①⑤は貴社の非財務財務化戦略の骨子が固まってから着手すべきであり、今回は②③④の土台を固める設計にした」等、戦略的根拠を明確に示せる。
+危: 「専門外です」と能力の限界を認める、または理由なく「対応可能です」と安易に拡張を約束する（スコープ規律のなさを示す）。</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>①⑤を含めた場合の追加人員・金額・期間を、この場で概算で示してください。</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>戦略的な判断なら、なぜその判断根拠を提案書のどこにも明記していないのですか。当社が①⑤への貴社の関与を過小に見積もるリスクを、貴社はどう考えていましたか。</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>C社: アビームコンサルティングへの個別質問</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="150" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="150" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>【v1.1反映】基本スコープ5,300万円（オプションA/B分離済み）について、ランク別単価×人数×稼働率×期間の内訳を提出してください。あわせて、基本スコープの各タスク（#1〜#10、#12の一部）と内訳の対応表を示し、どのタスクに最も工数を要しているかを明示してください。</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>分離自体は完了済みだが、なお5,300万円が他社の1.6〜2.2倍である原因が「単価水準」か「投入人数・稼働率」かは、この内訳でしか切り分けられない。</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>良: 内訳つきで提出し、単価が他社と同水準（品質差で説明できる）か、単価自体が高い（品質と無関係な割高要因）かが判別できる。
 危: 総額のみで内訳を示さない、又はタスク対応が粗い。</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>最も工数を要するタスクはどれですか。そのタスクが期間内に完了しなかった場合、どのタスクの工数を削って吸収しますか。</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>内訳が出せない理由は何ですか。準委任契約で工数内訳が開示できないのは説明がつきません。開示なしで5,300万円の妥当性を当社はどう検証すればよいのですか。</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33" ht="150" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36" ht="150" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>RFP発行「年内」を11月末に前倒しできますか。ボトルネックは何ですか。前倒しのために当社が9月中に意思決定すべき事項を、優先順位付きで挙げてください。</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>2028/1逆算を掲げる同社が「12月で間に合う」と考えるなら、その根拠を数字で語らせる。合理的なら当社計画の見直し材料にもなる。</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>良: 前倒しの条件（当社の意思決定期限・削る要素）を具体的に提示、または12月案の合理性を逆線表で証明。
 危: 「調整可能です」のみ。ボトルネックを特定できない。</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>11月末発行の前倒し案において、当社が9月中に決められなかった場合の縮退ルール（どの要件を条件付きに落とすか）を事前合意できますか。</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>「12月で間に合う」根拠の逆線表で、ベンダー評価が1月末に完了しなかった場合（回答遅延・再質疑）のバッファはどこにありますか。2027年中構築完了のクリティカルパスには何日の余裕がありますか。</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr"/>
-      <c r="J33" s="10" t="inlineStr"/>
-    </row>
-    <row r="34" ht="150" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr"/>
+      <c r="J36" s="10" t="inlineStr"/>
+    </row>
+    <row r="37" ht="150" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>中立性</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>御社はベンダー評価・選定までをスコープに含め、ソリューションベンダーとのリレーションを強みとして挙げています。後続の導入フェーズを御社自身が受注する意思はありますか。ある場合、要件定義・RFP・評価軸が御社の得意なソリューションや自社導入体制に有利に働かないことをどう担保しますか。</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>「RFPを書く者が選定も行い、導入も狙う」構造は最も利益相反が起きやすい。導入受注の意思を先に言質として取る。</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>良: 受注意思の有無を明言し、ある場合は評価から自社を外す設計に同意。
 危: 「その時点で検討」（意思を曖昧にしたまま選定に関与し続ける）。</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>導入を受注しないと明言できるなら、それを契約書（入札制限条項）に明記できますか。受注可能性を残すなら、ベンダー評価プロセスから御社を外し「当社＋第三者評価」とする設計に同意しますか。</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>「中立評価」の実績として、御社リレーション外のベンダーが選定された割合を開示してください。RFP発出先リストの選定基準は誰が作り、誰が承認しますか。</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr"/>
-      <c r="J34" s="10" t="inlineStr"/>
-    </row>
-    <row r="35" ht="150" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38" ht="150" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>「参画メンバーは変更になる可能性があります」の注記を撤回し、主要5名（豊嶋・山野・平野・張本・今野の各氏）の稼働率%・期間中の交代禁止（または交代時の品質担保条件）を確約できますか。また、SGホールディングス案件等、同時期に走る大型案件との要員重複はありませんか。</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>実名の豪華さと実際の稼働は別物。特にプリンシパル・ダイレクター級の実稼働%を数字で確定させる。</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>良: 月別稼働率%と交代条件を書面で確約。重複を正直に開示。
 危: 注記を維持したまま「基本的には変わりません」。アドバイザーの稼働が「適宜」のまま。</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>プリンシパル・ダイレクター級は実質週何時間を本件に使いますか。定例会議出席以外の実働（成果物レビュー時間）をコミットできますか。</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>注記を撤回できない理由は何ですか。交代時に「同等以上のランク・類似経験者を当社承認のうえ配置」する条項を契約に入れられますか。</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr"/>
-      <c r="J35" s="10" t="inlineStr"/>
-    </row>
-    <row r="36" ht="150" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr"/>
+      <c r="J38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39" ht="150" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>C4/Q4</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>「工数削減額・リスク回避額・収益機会」の効果3分類について、過去案件で経営会議が実際に投資承認した試算の実例を1件、数字の粒度が分かる形で紹介してください（社名は伏せて構いません）。「CFP即応が受注シェアに直結」という仮説の根拠となるデータはありますか。</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>攻めのストーリーが「営業トーク」か「再現可能な方法論」かの見極め。</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>良: 実例の試算構造（前提・データソース・金額規模）を具体的に説明。
 危: フレームワークの説明に終始し実例が出ない。</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>その実例の試算ロジックを本件に適用した場合、当社のROI試算はいつ時点で・どの精度で出せますか。当社の経営上申（投資承認）のタイミングとどう整合させますか。</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>実例が出せないなら、効果3分類は概念に留まります。数億円規模になる基盤構築の投資判断を支える定量根拠を、この要件定義期間中に・どのデータで作るのか説明してください。</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr"/>
-      <c r="J36" s="10" t="inlineStr"/>
-    </row>
-    <row r="37" ht="150" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr"/>
+      <c r="J39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40" ht="150" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>★C6</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>Q2/Q5</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>「戦略依存×Must/Should/Could」の4象限と二層整理（共通要件＋テーマ別シナリオ）を適用した過去案件で、①線引きの判断が貴社とクライアントで割れた実例と収拾方法、②戦略確定後に実際にRFP要件がどれだけ変わったか（変更件数・変更率）を教えてください。</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>書面で最高評価（Q2素点5）をつけた中核方法論の実効性検証。素点5は「裏付け完全」が要件のため、高得点ほど質疑での検証が必須。方法論が本当に手戻りを減らしたのかをアウトカム（変更率）で証明させる。</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>良: 割れた実例を率直に語り、変更率を数字で示せる（例: 戦略確定後の要件変更が全体の○%に収まり、うち構造変更はゼロ等）。
 危: 「うまくいきました」のみで数字なし。割れた実例が「ない」（適用実績が浅いか、都合の悪い情報を出さない）。</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>本件でMust×戦略非依存の「骨格」に置くと仰る組織マスタ・証憑統制・Scope1/2算定のうち、実は当社の戦略次第で動き得るものはどれですか。骨格の線引きを最初の何週で当社と合意しますか。</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t>変更率のデータがないなら、「手戻り最小化」の効果は測定されていない主張になります。本件では何をもって「手戻りが最小化された」と評価すればよいか、測定可能な形で定義してください。</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr"/>
-      <c r="J37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38" ht="150" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr"/>
+      <c r="J40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41" ht="150" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>★C7</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>当社にて成果物を照合したところ、PwC社の27,000,000円の見積り（3.6ヶ月）には「開示効率化検討」「展開計画・定着計画」「PJ計画書」が含まれていますが、貴社の基本スコープ5,300万円（3.9ヶ月）にはこれらが含まれず、オプションBに切り出されています。つまり貴社の基本スコープは他社より成果物が狭いにもかかわらず、価格はPwC社の約2倍です。この差の主因は単価水準ですか、投入人数ですか。ランク別内訳（C1の宿題回答）でご説明ください。</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>最も鋭い一問。品質でもスコープでも説明のつかない価格差（超過コスト）を、貴社自身に他社比較で直接答えさせる。回避不能な形で単価水準の説明責任を負わせる。</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>良: 単価が他社より高い理由を明確に説明（シニアリティ、専門性、リスクプレミアム等）し、その根拠を具体的な数字・実例で示す。
 危: 「価値が違います」等の定性論で数字を出さない。他社見積りの前提を問題にして自社の説明を回避する。</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>その単価差に見合う成果（例: 手戻りゼロ、保証人指摘ゼロ）を過去案件で実現した実例はありますか。本件でその成果を測定可能な形で契約に落とし込めますか。</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t>説明できないなら、貴社の基本スコープ価格は市場価格から外れている可能性があります。PwC社の27,000,000円の内容に貴社の強み（2段階アーキテクチャ・独立データ要件定義書）を追加した場合の増分見積りを、この場で概算で示してください。</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr"/>
-      <c r="J38" s="10" t="inlineStr"/>
-    </row>
-    <row r="39" ht="150" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr"/>
+      <c r="J41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42" ht="150" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>★C8</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Q3/Q4/Q6</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>アドバイザーの森銅様は、SSBJ対応向けシステム要件定義・導入実績（物流業・化学メーカー・非鉄金属メーカー等）を複数お持ちと理解しています。この方の本件での実稼働率は体制表で「適宜」とありますが、具体的に週何時間、基本スコープのどのタスク（#4システム構成案策定・#8システム要件定義等）を担当されますか。また、攻め側（#2出口設計のユースケース優先順位付け）を主導するのはどなたですか、その方の類似実績を教えてください。</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>貴社の体制で最もシステム連携・SSBJシステム導入の実務経験が濃い人物（森銅様）が「適宜」という低稼働の位置づけになっている。守り担当（森銅様）と攻め担当が明確に分かれているか、それぞれの実働時間を具体的に確認する。</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>良: 森銅様の週次稼働時間とタスク対応を具体的に提示し、攻め担当者（別人物）の実例も明示。
 危: 「必要に応じて随時サポートします」（稼働時間・タスク対応が不明確）。</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>森銅様が「適宜」ではなく特定タスク（#4・#8等）に固定的にコミットする形に変更できますか。その場合の稼働率%と体制表の更新版を提出してください。</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>「適宜」のままだと、基本スコープの技術的な品質は山野様（マネージャー）と平野様（シニアコンサルタント）と貴社選定のコンサルタント3名（人数調整）に依存することになります。この体制でシステム構成案（#4）の技術的妥当性を担保できる根拠を示してください。</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr"/>
-      <c r="J39" s="10" t="inlineStr"/>
+      <c r="I42" s="10" t="inlineStr"/>
+      <c r="J42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43" ht="150" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>★C9</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Q1/Q2</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>貴社提案書には、難所①（ルールの策定）について、業務要件検討の前提として「事前にLION様にて策定済みと想定」（P.28）とする記述と、出口設計（#2）でMust/Should/Could×戦略依存の6象限により線引き合意を最上流の意思決定点に設計する（P.26）という記述の両方が存在します。難所①は貴社が能動的に検討・確定を主導するのか、それとも当社が既に確定済みという前提で臨むのか、どちらですか。</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>提案書内の矛盾を解消する。前提化（L0）なら難所①は実質スコープに含まれず、方法論適用（L2〜L3）なら含まれる——この違いはQ1・Q2の確定素点、および「なぜこの作業が53,000,000円の基本スコープに入っているか」という価格妥当性の双方に影響する。</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>良: 「制度上確定済みの部分（組織境界の一次案等）は前提とし、戦略変動に応じた線引き調整の部分は6象限方法論で能動的に検討する」等、前提とする部分と方法論で検討する部分の境界を明確に整理できる。
+危: 矛盾を認めない、または矛盾自体に気づいていない。</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>前提とする部分と方法論で検討する部分の境界線を、今この場で具体的に示してください。当社が「策定済み」と誤解している範囲はどこですか。</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>矛盾を解消できないなら、貴社は難所①への対応方針を固めきれていないことになります。この状態のまま、当社は53,000,000円の基本スコープの妥当性をどう判断すればよいですか。</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A15:J15"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A25:J25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/コンペ質疑_質問票.xlsx
+++ b/docs/コンペ質疑_質問票.xlsx
@@ -1756,7 +1756,9 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>御見積書の案②（27,000,000円）には「1-4 業務要件定義書作成」1タスクのみが業務要件側の記載ですが、当社が別途照合したところ、機能要件定義書・データ要件定義書・システム要件定義書に相当する独立した記載が価格表上で確認できません。①これらは1-4に含まれますか、②含まれないなら追加のタスク・金額が必要ですか、を明確にしてください。</t>
+          <t>貴社の御見積書（案②：27,000,000円）を拝見したところ、業務要件に関するタスクは「1-4 業務要件定義書作成」の1行のみとなっております。当社が想定している成果物には、業務要件定義書のほかに、機能要件定義書・データ要件定義書・システム要件定義書もそれぞれ独立した文書として含まれておりますが、これらが「1-4 業務要件定義書作成」に含まれているのかどうか、価格表上では判断がつきませんでした。恐れ入りますが、以下の2点についてご教示いただけますでしょうか。
+①機能要件定義書・データ要件定義書・システム要件定義書は、案②（27,000,000円）の見積り範囲に含まれていますか。含まれる場合、それぞれどの程度の粒度で作成いただけますか。
+②含まれない場合、追加で作成いただくとしたら、どのようなタスクが追加になり、金額はどの程度になりますか。</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -1772,12 +1774,12 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>機能要件定義書を独立文書として発行することは可能ですか。その場合、貴社の成果物マッピング表（P.40）に記載の「システム機能要求一覧」等との対応関係を教えてください。</t>
+          <t>機能要件定義書を独立した文書として発行いただくことは可能でしょうか。可能な場合、貴社の成果物マッピング表（P.40）に記載の「システム機能要求一覧」等とどのように対応するか、教えていただけますでしょうか。</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>含まれないなら、案②の27,000,000円は当社が想定する成果物10点を満たしていない可能性があります。満たすための追加金額を今この場で概算で示してください。</t>
+          <t>含まれない場合、案②の27,000,000円では当社が想定する成果物を満たさない可能性があります。恐れ入りますが、満たすために必要な追加金額の概算を、この場でお示しいただけますでしょうか。</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr"/>

--- a/docs/コンペ質疑_質問票.xlsx
+++ b/docs/コンペ質疑_質問票.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検（第1回）で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。⑦アビームv1.1改訂（基本/オプション分離）と成果物カバレッジ照合（第2回再点検）を反映しC1・★A7・★B6・★C7を追加/更新。スコープ差は双方向（アビームが広い部分／PwC案②が広い部分の両方が存在）のため、価格差を単純にスコープや品質だけで説明させない設計。⑧第3回再点検: アサインメンバーの経歴を「攻め／守り」の技術専門性（システム連携・API連携経験等）で照合し、★共8・★A8・★B7・★C8を追加。Q6は実名・経歴の有無までしか採点していないため、本件の技術判断に耐える経験の有無と、その人物が実働で入るか（アドバイザー止まりでないか）を別途確認する。⑨第4回再点検: 5つの難所（貴社RFP由来の共通言語）×深さレベル（L0前提化〜L4詳細設計）×担当で3社を独立照合した結果を踏まえ、★共9（自己採点による照合）・★A9（ライズの深さの天井を即答で検証）・★B8（PwCの前提化・後ろ倒しが戦略判断か能力の限界か）・★C9（アビーム提案書内の難所①に関する記述矛盾の解消）を追加。</t>
+          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検（第1回）で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。⑦アビームv1.1改訂（基本/オプション分離）と成果物カバレッジ照合（第2回再点検）を反映しC1・★A7・★B6・★C7を追加/更新。スコープ差は双方向（アビームが広い部分／PwC案②が広い部分の両方が存在）のため、価格差を単純にスコープや品質だけで説明させない設計。⑧第3回再点検: アサインメンバーの経歴を「攻め／守り」の技術専門性（システム連携・API連携経験等）で照合し、★共8・★A8・★B7・★C8を追加。Q6は実名・経歴の有無までしか採点していないため、本件の技術判断に耐える経験の有無と、その人物が実働で入るか（アドバイザー止まりでないか）を別途確認する。⑨第4回再点検: 5つの難所（貴社RFP由来の共通言語）×深さレベル（L0前提化〜L4詳細設計）×担当で3社を独立照合した結果を踏まえ、★共9（自己採点による照合）・★A9（ライズの深さの天井を即答で検証）・★B8（PwCの前提化・後ろ倒しが戦略判断か能力の限界か）・★C9（アビーム提案書内の難所①に関する記述矛盾の解消）を追加。⑩第5回再点検: 弊社依頼事項（攻め・守り）とPwC提案書を1行ずつ照合した結果、PwC自身が「ご依頼事項（PwC理解）」（P.10）で正確に理解を示している『攻め』の2本柱（Scope3一次データ改革・CFP開示スキーム）が、実行計画（P.28）では両方ともStep2以降に後ろ倒しになっている自己矛盾を発見。★B9（この矛盾を直接突く）・★B10（自ら追加提起した難所⑦と実行タスクの深さの不釣り合いを突く）を追加。</t>
         </is>
       </c>
     </row>
@@ -1875,431 +1875,521 @@
       <c r="I33" s="10" t="inlineStr"/>
       <c r="J33" s="10" t="inlineStr"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="34" ht="150" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>★B9</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Q1/Q4</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>貴社の「2-1. ご依頼事項（PwC理解）」（P.10）では、当社の依頼事項のうち『攻め』の柱として『Scope3の1次データ置き換えを含む、サプライチェーン全体の改革』と『CFP開示における顧客要請への対応（データ収集から算定開示までのスキーム構築）』を明記されています。一方、貴社の業務要件検討の進め方（P.28）では、データ収集について『サプライヤー連携はStep2以降実施』と明記されており、CFPに関するタスクも本フェーズの成果物一覧には見当たりません。当社の依頼事項として正しくご理解いただいている『攻め』の2つの柱が、なぜ本フェーズの実行計画には反映されていないのでしょうか。ご説明いただけますでしょうか。</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>提案書内の自己矛盾を直接突く、今回最も鋭い一問。P.10で正確に理解を示しながらP.28の実行計画では両方とも後ろ倒しにしているのは、「理解はあるが実行する体制・意思がない」のか「理解した上で意図的に段階分けした」のかを見極める。</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>良: 「Scope3一次データとCFPは、まず骨格（難所①③④）を固めてからでないと拡張要件として設計できないため、本フェーズでは将来の拡張を見据えた基盤要件の定義までを行い、Step2で本格実装する設計にしている」等、依頼事項の重要性を認識した上での戦略的な段階分けを具体的に説明できる。
+危: 「対応可能です」と安易に前言を撤回する（スコープ規律の欠如）。または「Step2の話です」とだけ回答し、P.10とP.28の記載の矛盾そのものには答えない。</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>「本フェーズでは基盤要件の定義まで行う」とのお答えでしたら、具体的にどのような基盤要件（データモデル・API連携方式等）を今回のRFPに含めていただければ、Step2でのScope3・CFP拡張を手戻りなく実現できますか。3点ほど教えてください。</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>「対応可能です」とのお答えでしたら、追加の人員・金額・期間はどう変わりますか。あわせて、なぜ提案書では本フェーズのスコープ外と明記されていたのか、今回のご回答と提案書の記載のどちらを当社は信じればよいか、教えてください。</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr"/>
+      <c r="J34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35" ht="150" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>★B10</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>貴社は当初の5つの難所に加え、独自に『難所⑦策定したルール・プロセス・システムの全世界拠点への定着』を追加され（P.11）、言語・商慣習・ITリテラシー・組織文化が異なる拠点への定着課題を指摘されています。一方、御見積書における対応タスクは『3-1 展開計画・基本方針作成』『3-2 計画書作成』の2行に見えます。恐れ入りますが、この2つのタスクで、貴社が自らご指摘された難易度にどのように対応いただけるのか、具体的に教えていただけますでしょうか。</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>PwCが自ら「重要な難所」として追加提起したにもかかわらず、対応する実行タスクの深さが不釣り合いに小さい可能性を検証する。難所を発見する分析力と、それを解決する実行力が一致しているかを見る一問。</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>良: 「3-1で拠点特性（言語・ITリテラシー等）別のセグメンテーションを行い、3-2でセグメント別の展開順序・ローカル裁量の権限設計まで行う」等、2行のタスクの中身を具体的に説明できる。
+危: 「詳細は次工程で検討します」（難所の指摘が分析上のアピールに留まり、実行計画には反映されていない可能性）。</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>全世界拠点への定着において、本社統制とローカル裁量のバランス設計は、成果物（業務要件定義書）のどの章に落とし込まれますか。</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>2行のタスクで対応しきれないということでしたら、難所⑦は実質的に本フェーズのスコープ外ということになります。その場合、当社は次フェーズでこの難所にどのように備えるべきでしょうか。追加のお見積りは必要でしょうか。</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>C社: アビームコンサルティングへの個別質問</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="150" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="150" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>【v1.1反映】基本スコープ5,300万円（オプションA/B分離済み）について、ランク別単価×人数×稼働率×期間の内訳を提出してください。あわせて、基本スコープの各タスク（#1〜#10、#12の一部）と内訳の対応表を示し、どのタスクに最も工数を要しているかを明示してください。</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>分離自体は完了済みだが、なお5,300万円が他社の1.6〜2.2倍である原因が「単価水準」か「投入人数・稼働率」かは、この内訳でしか切り分けられない。</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>良: 内訳つきで提出し、単価が他社と同水準（品質差で説明できる）か、単価自体が高い（品質と無関係な割高要因）かが判別できる。
 危: 総額のみで内訳を示さない、又はタスク対応が粗い。</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>最も工数を要するタスクはどれですか。そのタスクが期間内に完了しなかった場合、どのタスクの工数を削って吸収しますか。</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>内訳が出せない理由は何ですか。準委任契約で工数内訳が開示できないのは説明がつきません。開示なしで5,300万円の妥当性を当社はどう検証すればよいのですか。</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr"/>
-      <c r="J35" s="10" t="inlineStr"/>
-    </row>
-    <row r="36" ht="150" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38" ht="150" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>RFP発行「年内」を11月末に前倒しできますか。ボトルネックは何ですか。前倒しのために当社が9月中に意思決定すべき事項を、優先順位付きで挙げてください。</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>2028/1逆算を掲げる同社が「12月で間に合う」と考えるなら、その根拠を数字で語らせる。合理的なら当社計画の見直し材料にもなる。</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>良: 前倒しの条件（当社の意思決定期限・削る要素）を具体的に提示、または12月案の合理性を逆線表で証明。
 危: 「調整可能です」のみ。ボトルネックを特定できない。</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>11月末発行の前倒し案において、当社が9月中に決められなかった場合の縮退ルール（どの要件を条件付きに落とすか）を事前合意できますか。</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>「12月で間に合う」根拠の逆線表で、ベンダー評価が1月末に完了しなかった場合（回答遅延・再質疑）のバッファはどこにありますか。2027年中構築完了のクリティカルパスには何日の余裕がありますか。</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr"/>
-      <c r="J36" s="10" t="inlineStr"/>
-    </row>
-    <row r="37" ht="150" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr"/>
+      <c r="J38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39" ht="150" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>中立性</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>御社はベンダー評価・選定までをスコープに含め、ソリューションベンダーとのリレーションを強みとして挙げています。後続の導入フェーズを御社自身が受注する意思はありますか。ある場合、要件定義・RFP・評価軸が御社の得意なソリューションや自社導入体制に有利に働かないことをどう担保しますか。</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>「RFPを書く者が選定も行い、導入も狙う」構造は最も利益相反が起きやすい。導入受注の意思を先に言質として取る。</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>良: 受注意思の有無を明言し、ある場合は評価から自社を外す設計に同意。
 危: 「その時点で検討」（意思を曖昧にしたまま選定に関与し続ける）。</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>導入を受注しないと明言できるなら、それを契約書（入札制限条項）に明記できますか。受注可能性を残すなら、ベンダー評価プロセスから御社を外し「当社＋第三者評価」とする設計に同意しますか。</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>「中立評価」の実績として、御社リレーション外のベンダーが選定された割合を開示してください。RFP発出先リストの選定基準は誰が作り、誰が承認しますか。</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr"/>
-      <c r="J37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38" ht="150" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr"/>
+      <c r="J39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40" ht="150" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>「参画メンバーは変更になる可能性があります」の注記を撤回し、主要5名（豊嶋・山野・平野・張本・今野の各氏）の稼働率%・期間中の交代禁止（または交代時の品質担保条件）を確約できますか。また、SGホールディングス案件等、同時期に走る大型案件との要員重複はありませんか。</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>実名の豪華さと実際の稼働は別物。特にプリンシパル・ダイレクター級の実稼働%を数字で確定させる。</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>良: 月別稼働率%と交代条件を書面で確約。重複を正直に開示。
 危: 注記を維持したまま「基本的には変わりません」。アドバイザーの稼働が「適宜」のまま。</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>プリンシパル・ダイレクター級は実質週何時間を本件に使いますか。定例会議出席以外の実働（成果物レビュー時間）をコミットできますか。</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t>注記を撤回できない理由は何ですか。交代時に「同等以上のランク・類似経験者を当社承認のうえ配置」する条項を契約に入れられますか。</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr"/>
-      <c r="J38" s="10" t="inlineStr"/>
-    </row>
-    <row r="39" ht="150" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr"/>
+      <c r="J40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41" ht="150" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>C4/Q4</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>「工数削減額・リスク回避額・収益機会」の効果3分類について、過去案件で経営会議が実際に投資承認した試算の実例を1件、数字の粒度が分かる形で紹介してください（社名は伏せて構いません）。「CFP即応が受注シェアに直結」という仮説の根拠となるデータはありますか。</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>攻めのストーリーが「営業トーク」か「再現可能な方法論」かの見極め。</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>良: 実例の試算構造（前提・データソース・金額規模）を具体的に説明。
 危: フレームワークの説明に終始し実例が出ない。</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>その実例の試算ロジックを本件に適用した場合、当社のROI試算はいつ時点で・どの精度で出せますか。当社の経営上申（投資承認）のタイミングとどう整合させますか。</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t>実例が出せないなら、効果3分類は概念に留まります。数億円規模になる基盤構築の投資判断を支える定量根拠を、この要件定義期間中に・どのデータで作るのか説明してください。</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr"/>
-      <c r="J39" s="10" t="inlineStr"/>
-    </row>
-    <row r="40" ht="150" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr"/>
+      <c r="J41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42" ht="150" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>★C6</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Q2/Q5</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>「戦略依存×Must/Should/Could」の4象限と二層整理（共通要件＋テーマ別シナリオ）を適用した過去案件で、①線引きの判断が貴社とクライアントで割れた実例と収拾方法、②戦略確定後に実際にRFP要件がどれだけ変わったか（変更件数・変更率）を教えてください。</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>書面で最高評価（Q2素点5）をつけた中核方法論の実効性検証。素点5は「裏付け完全」が要件のため、高得点ほど質疑での検証が必須。方法論が本当に手戻りを減らしたのかをアウトカム（変更率）で証明させる。</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>良: 割れた実例を率直に語り、変更率を数字で示せる（例: 戦略確定後の要件変更が全体の○%に収まり、うち構造変更はゼロ等）。
 危: 「うまくいきました」のみで数字なし。割れた実例が「ない」（適用実績が浅いか、都合の悪い情報を出さない）。</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>本件でMust×戦略非依存の「骨格」に置くと仰る組織マスタ・証憑統制・Scope1/2算定のうち、実は当社の戦略次第で動き得るものはどれですか。骨格の線引きを最初の何週で当社と合意しますか。</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>変更率のデータがないなら、「手戻り最小化」の効果は測定されていない主張になります。本件では何をもって「手戻りが最小化された」と評価すればよいか、測定可能な形で定義してください。</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr"/>
-      <c r="J40" s="10" t="inlineStr"/>
-    </row>
-    <row r="41" ht="150" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr"/>
+      <c r="J42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43" ht="150" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>★C7</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>当社にて成果物を照合したところ、PwC社の27,000,000円の見積り（3.6ヶ月）には「開示効率化検討」「展開計画・定着計画」「PJ計画書」が含まれていますが、貴社の基本スコープ5,300万円（3.9ヶ月）にはこれらが含まれず、オプションBに切り出されています。つまり貴社の基本スコープは他社より成果物が狭いにもかかわらず、価格はPwC社の約2倍です。この差の主因は単価水準ですか、投入人数ですか。ランク別内訳（C1の宿題回答）でご説明ください。</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>最も鋭い一問。品質でもスコープでも説明のつかない価格差（超過コスト）を、貴社自身に他社比較で直接答えさせる。回避不能な形で単価水準の説明責任を負わせる。</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>良: 単価が他社より高い理由を明確に説明（シニアリティ、専門性、リスクプレミアム等）し、その根拠を具体的な数字・実例で示す。
 危: 「価値が違います」等の定性論で数字を出さない。他社見積りの前提を問題にして自社の説明を回避する。</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>その単価差に見合う成果（例: 手戻りゼロ、保証人指摘ゼロ）を過去案件で実現した実例はありますか。本件でその成果を測定可能な形で契約に落とし込めますか。</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>説明できないなら、貴社の基本スコープ価格は市場価格から外れている可能性があります。PwC社の27,000,000円の内容に貴社の強み（2段階アーキテクチャ・独立データ要件定義書）を追加した場合の増分見積りを、この場で概算で示してください。</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr"/>
-      <c r="J41" s="10" t="inlineStr"/>
-    </row>
-    <row r="42" ht="150" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" s="10" t="inlineStr"/>
+    </row>
+    <row r="44" ht="150" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>★C8</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>Q3/Q4/Q6</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>アドバイザーの森銅様は、SSBJ対応向けシステム要件定義・導入実績（物流業・化学メーカー・非鉄金属メーカー等）を複数お持ちと理解しています。この方の本件での実稼働率は体制表で「適宜」とありますが、具体的に週何時間、基本スコープのどのタスク（#4システム構成案策定・#8システム要件定義等）を担当されますか。また、攻め側（#2出口設計のユースケース優先順位付け）を主導するのはどなたですか、その方の類似実績を教えてください。</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>貴社の体制で最もシステム連携・SSBJシステム導入の実務経験が濃い人物（森銅様）が「適宜」という低稼働の位置づけになっている。守り担当（森銅様）と攻め担当が明確に分かれているか、それぞれの実働時間を具体的に確認する。</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F44" s="9" t="inlineStr">
         <is>
           <t>良: 森銅様の週次稼働時間とタスク対応を具体的に提示し、攻め担当者（別人物）の実例も明示。
 危: 「必要に応じて随時サポートします」（稼働時間・タスク対応が不明確）。</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G44" s="9" t="inlineStr">
         <is>
           <t>森銅様が「適宜」ではなく特定タスク（#4・#8等）に固定的にコミットする形に変更できますか。その場合の稼働率%と体制表の更新版を提出してください。</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H44" s="9" t="inlineStr">
         <is>
           <t>「適宜」のままだと、基本スコープの技術的な品質は山野様（マネージャー）と平野様（シニアコンサルタント）と貴社選定のコンサルタント3名（人数調整）に依存することになります。この体制でシステム構成案（#4）の技術的妥当性を担保できる根拠を示してください。</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr"/>
-      <c r="J42" s="10" t="inlineStr"/>
-    </row>
-    <row r="43" ht="150" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr"/>
+      <c r="J44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45" ht="150" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>★C9</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>Q1/Q2</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>貴社提案書には、難所①（ルールの策定）について、業務要件検討の前提として「事前にLION様にて策定済みと想定」（P.28）とする記述と、出口設計（#2）でMust/Should/Could×戦略依存の6象限により線引き合意を最上流の意思決定点に設計する（P.26）という記述の両方が存在します。難所①は貴社が能動的に検討・確定を主導するのか、それとも当社が既に確定済みという前提で臨むのか、どちらですか。</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>提案書内の矛盾を解消する。前提化（L0）なら難所①は実質スコープに含まれず、方法論適用（L2〜L3）なら含まれる——この違いはQ1・Q2の確定素点、および「なぜこの作業が53,000,000円の基本スコープに入っているか」という価格妥当性の双方に影響する。</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>良: 「制度上確定済みの部分（組織境界の一次案等）は前提とし、戦略変動に応じた線引き調整の部分は6象限方法論で能動的に検討する」等、前提とする部分と方法論で検討する部分の境界を明確に整理できる。
 危: 矛盾を認めない、または矛盾自体に気づいていない。</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>前提とする部分と方法論で検討する部分の境界線を、今この場で具体的に示してください。当社が「策定済み」と誤解している範囲はどこですか。</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t>矛盾を解消できないなら、貴社は難所①への対応方針を固めきれていないことになります。この状態のまま、当社は53,000,000円の基本スコープの妥当性をどう判断すればよいですか。</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr"/>
-      <c r="J43" s="10" t="inlineStr"/>
+      <c r="I45" s="10" t="inlineStr"/>
+      <c r="J45" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A36:J36"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A2:J2"/>

--- a/docs/コンペ質疑_質問票.xlsx
+++ b/docs/コンペ質疑_質問票.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検（第1回）で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。⑦アビームv1.1改訂（基本/オプション分離）と成果物カバレッジ照合（第2回再点検）を反映しC1・★A7・★B6・★C7を追加/更新。スコープ差は双方向（アビームが広い部分／PwC案②が広い部分の両方が存在）のため、価格差を単純にスコープや品質だけで説明させない設計。⑧第3回再点検: アサインメンバーの経歴を「攻め／守り」の技術専門性（システム連携・API連携経験等）で照合し、★共8・★A8・★B7・★C8を追加。Q6は実名・経歴の有無までしか採点していないため、本件の技術判断に耐える経験の有無と、その人物が実働で入るか（アドバイザー止まりでないか）を別途確認する。⑨第4回再点検: 5つの難所（貴社RFP由来の共通言語）×深さレベル（L0前提化〜L4詳細設計）×担当で3社を独立照合した結果を踏まえ、★共9（自己採点による照合）・★A9（ライズの深さの天井を即答で検証）・★B8（PwCの前提化・後ろ倒しが戦略判断か能力の限界か）・★C9（アビーム提案書内の難所①に関する記述矛盾の解消）を追加。⑩第5回再点検: 弊社依頼事項（攻め・守り）とPwC提案書を1行ずつ照合した結果、PwC自身が「ご依頼事項（PwC理解）」（P.10）で正確に理解を示している『攻め』の2本柱（Scope3一次データ改革・CFP開示スキーム）が、実行計画（P.28）では両方ともStep2以降に後ろ倒しになっている自己矛盾を発見。★B9（この矛盾を直接突く）・★B10（自ら追加提起した難所⑦と実行タスクの深さの不釣り合いを突く）を追加。</t>
+          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検（第1回）で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。⑦アビームv1.1改訂（基本/オプション分離）と成果物カバレッジ照合（第2回再点検）を反映しC1・★A7・★B6・★C7を追加/更新。スコープ差は双方向（アビームが広い部分／PwC案②が広い部分の両方が存在）のため、価格差を単純にスコープや品質だけで説明させない設計。⑧第3回再点検: アサインメンバーの経歴を「攻め／守り」の技術専門性（システム連携・API連携経験等）で照合し、★共8・★A8・★B7・★C8を追加。Q6は実名・経歴の有無までしか採点していないため、本件の技術判断に耐える経験の有無と、その人物が実働で入るか（アドバイザー止まりでないか）を別途確認する。⑨第4回再点検: 5つの難所（貴社RFP由来の共通言語）×深さレベル（L0前提化〜L4詳細設計）×担当で3社を独立照合した結果を踏まえ、★共9（自己採点による照合）・★A9（ライズの深さの天井を即答で検証）・★B8（PwCの前提化・後ろ倒しが戦略判断か能力の限界か）・★C9（アビーム提案書内の難所①に関する記述矛盾の解消）を追加。⑩第5回再点検: 弊社依頼事項（攻め・守り）とPwC提案書を1行ずつ照合した結果、PwC自身が「ご依頼事項（PwC理解）」（P.10）で正確に理解を示している『攻め』の2本柱（Scope3一次データ改革・CFP開示スキーム）が、実行計画（P.28）では両方ともStep2以降に後ろ倒しになっている自己矛盾を発見。★B9（この矛盾を直接突く）・★B10（自ら追加提起した難所⑦と実行タスクの深さの不釣り合いを突く）を追加。⑪第6回再点検: P.39「アプローチ想定作成物」の図面を精査した結果、①攻め系の成果物ボックスが図全体に1つも存在せず★B9の指摘を構造面で裏付け、②新業務定着の箱が2つのみで★B10を裏付け、③「提案スコープ」点線の境界（開示戦略策定・RFP作成・アーキテクチャ素案が内外どちらか）が判読困難、④RFP作成が全ワークストリームの統合点＝クリティカルパス集中構造、という新たな発見。③④について★B11・★B12を追加。</t>
         </is>
       </c>
     </row>
@@ -1965,433 +1965,523 @@
       <c r="I35" s="10" t="inlineStr"/>
       <c r="J35" s="10" t="inlineStr"/>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="36" ht="150" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>★B11</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>C1/D2</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>貴社の「4-1. アプローチ想定作成物」（P.39）を拝見しました。凡例では「提案スコープ」を点線の枠で示すとされていますが、図を拝見すると、開示戦略策定／開示内容整理・算定ガイドライン更新（左上のブロック）や、RFP作成そのものが、点線の内側なのか外側なのか、当社では判読が難しく感じました。恐れ入りますが、①開示戦略策定・算定ガイドライン更新の一連の作業（リスク機会特定・開示項目特定等）、②RFP作成、③アーキテクチャ素案作成は、それぞれ「提案スコープ」の点線の内側でしょうか、外側でしょうか。図の上で明確にお示しいただけますでしょうか。</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>提案書の中核スライドでスコープの境界線自体が判読しづらいのは、当社が金額の妥当性を検証する上で大きな障害になる。この図1枚でスコープの全体像を確定させることで、C1（見積総額の妥当性）・D2（成果物完遂のコミット）双方の判断材料を得る。</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>良: 点線の範囲を明確に言語化し、境界にある成果物（RFP作成・アーキテクチャ素案等）の内外を即答できる。
+危: 「基本的に全体を含みます」等、図の点線の意味を曖昧にしたまま回答する。</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>（境界が曖昧と判明した場合）今回提示いただいた図を、点線の範囲を明確化した改訂版として再提出いただけますでしょうか。</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>点線の範囲を明確にできないなら、貴社の27,000,000円（案②）がこの図のどこまでをカバーするのか、当社は確定できません。価格の妥当性を検証できない状態のまま、当社は貴社を評価することになります。</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr"/>
+      <c r="J36" s="10" t="inlineStr"/>
+    </row>
+    <row r="37" ht="150" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>★B12</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>D1/D4</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>同じくP.39の図について伺います。RFP作成は、業務要件定義書・システム機能要求一覧・システム非機能要求一覧・移行運用要求一覧・開示レポート一覧・アーキテクチャ素案・PJ計画書・展開方針という、ほぼ全てのワークストリームの出力を統合する単一の終着点として設計されているように見えます。この設計はRFPの一貫性を高める一方で、いずれか1つのワークストリームが遅延すればRFP発行全体が遅延するという、スケジュール上の単一障害点（クリティカルパスの集中）を内包しているように見えます。この集中リスクを、貴社はどのように管理される予定でしょうか（例えば、確定した部分から先行してRFPの一部を発出することは可能でしょうか）。</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>RFP作成を統合ポイントとする設計自体は評価できるが、裏を返せば依存関係の集中というリスクでもある。この設計上のトレードオフをPwC自身が認識し、緩和策を持っているかを検証する。</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>良: 段階的なRFP発出（確定部分の先行発出、条件付き要件としての後続反映等、ライズが採用している考え方に近い工夫）や、ワークストリームごとの独立したバッファ設定など、具体的な緩和策を即答できる。
+危: 「進捗管理を徹底します」等、集中リスクそのものへの構造的な対策ではない一般論に終始する。</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>最も遅延しやすいワークストリームはどれだと想定していますか（例：保証人コミュニケーションを含む内部統制対応等）。そのワークストリームに追加のバッファを確保する計画はありますか。</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>緩和策がないなら、貴社の見積り期間（3.6ヶ月）は、最も遅いワークストリームの遅延をそのまま吸収する設計になっていないことになります。当社はこのスケジュールリスクをどう評価すればよいでしょうか。</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>C社: アビームコンサルティングへの個別質問</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="150" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="150" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>【v1.1反映】基本スコープ5,300万円（オプションA/B分離済み）について、ランク別単価×人数×稼働率×期間の内訳を提出してください。あわせて、基本スコープの各タスク（#1〜#10、#12の一部）と内訳の対応表を示し、どのタスクに最も工数を要しているかを明示してください。</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>分離自体は完了済みだが、なお5,300万円が他社の1.6〜2.2倍である原因が「単価水準」か「投入人数・稼働率」かは、この内訳でしか切り分けられない。</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>良: 内訳つきで提出し、単価が他社と同水準（品質差で説明できる）か、単価自体が高い（品質と無関係な割高要因）かが判別できる。
 危: 総額のみで内訳を示さない、又はタスク対応が粗い。</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>最も工数を要するタスクはどれですか。そのタスクが期間内に完了しなかった場合、どのタスクの工数を削って吸収しますか。</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>内訳が出せない理由は何ですか。準委任契約で工数内訳が開示できないのは説明がつきません。開示なしで5,300万円の妥当性を当社はどう検証すればよいのですか。</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr"/>
-      <c r="J37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38" ht="150" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr"/>
+      <c r="J39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40" ht="150" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>RFP発行「年内」を11月末に前倒しできますか。ボトルネックは何ですか。前倒しのために当社が9月中に意思決定すべき事項を、優先順位付きで挙げてください。</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>2028/1逆算を掲げる同社が「12月で間に合う」と考えるなら、その根拠を数字で語らせる。合理的なら当社計画の見直し材料にもなる。</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>良: 前倒しの条件（当社の意思決定期限・削る要素）を具体的に提示、または12月案の合理性を逆線表で証明。
 危: 「調整可能です」のみ。ボトルネックを特定できない。</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>11月末発行の前倒し案において、当社が9月中に決められなかった場合の縮退ルール（どの要件を条件付きに落とすか）を事前合意できますか。</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t>「12月で間に合う」根拠の逆線表で、ベンダー評価が1月末に完了しなかった場合（回答遅延・再質疑）のバッファはどこにありますか。2027年中構築完了のクリティカルパスには何日の余裕がありますか。</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr"/>
-      <c r="J38" s="10" t="inlineStr"/>
-    </row>
-    <row r="39" ht="150" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr"/>
+      <c r="J40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41" ht="150" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>中立性</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>御社はベンダー評価・選定までをスコープに含め、ソリューションベンダーとのリレーションを強みとして挙げています。後続の導入フェーズを御社自身が受注する意思はありますか。ある場合、要件定義・RFP・評価軸が御社の得意なソリューションや自社導入体制に有利に働かないことをどう担保しますか。</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>「RFPを書く者が選定も行い、導入も狙う」構造は最も利益相反が起きやすい。導入受注の意思を先に言質として取る。</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>良: 受注意思の有無を明言し、ある場合は評価から自社を外す設計に同意。
 危: 「その時点で検討」（意思を曖昧にしたまま選定に関与し続ける）。</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>導入を受注しないと明言できるなら、それを契約書（入札制限条項）に明記できますか。受注可能性を残すなら、ベンダー評価プロセスから御社を外し「当社＋第三者評価」とする設計に同意しますか。</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t>「中立評価」の実績として、御社リレーション外のベンダーが選定された割合を開示してください。RFP発出先リストの選定基準は誰が作り、誰が承認しますか。</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr"/>
-      <c r="J39" s="10" t="inlineStr"/>
-    </row>
-    <row r="40" ht="150" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr"/>
+      <c r="J41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42" ht="150" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>宿題</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Q6/D3</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>「参画メンバーは変更になる可能性があります」の注記を撤回し、主要5名（豊嶋・山野・平野・張本・今野の各氏）の稼働率%・期間中の交代禁止（または交代時の品質担保条件）を確約できますか。また、SGホールディングス案件等、同時期に走る大型案件との要員重複はありませんか。</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>実名の豪華さと実際の稼働は別物。特にプリンシパル・ダイレクター級の実稼働%を数字で確定させる。</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>良: 月別稼働率%と交代条件を書面で確約。重複を正直に開示。
 危: 注記を維持したまま「基本的には変わりません」。アドバイザーの稼働が「適宜」のまま。</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>プリンシパル・ダイレクター級は実質週何時間を本件に使いますか。定例会議出席以外の実働（成果物レビュー時間）をコミットできますか。</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>注記を撤回できない理由は何ですか。交代時に「同等以上のランク・類似経験者を当社承認のうえ配置」する条項を契約に入れられますか。</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr"/>
-      <c r="J40" s="10" t="inlineStr"/>
-    </row>
-    <row r="41" ht="150" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr"/>
+      <c r="J42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43" ht="150" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>C4/Q4</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>「工数削減額・リスク回避額・収益機会」の効果3分類について、過去案件で経営会議が実際に投資承認した試算の実例を1件、数字の粒度が分かる形で紹介してください（社名は伏せて構いません）。「CFP即応が受注シェアに直結」という仮説の根拠となるデータはありますか。</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>攻めのストーリーが「営業トーク」か「再現可能な方法論」かの見極め。</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>良: 実例の試算構造（前提・データソース・金額規模）を具体的に説明。
 危: フレームワークの説明に終始し実例が出ない。</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>その実例の試算ロジックを本件に適用した場合、当社のROI試算はいつ時点で・どの精度で出せますか。当社の経営上申（投資承認）のタイミングとどう整合させますか。</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>実例が出せないなら、効果3分類は概念に留まります。数億円規模になる基盤構築の投資判断を支える定量根拠を、この要件定義期間中に・どのデータで作るのか説明してください。</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr"/>
-      <c r="J41" s="10" t="inlineStr"/>
-    </row>
-    <row r="42" ht="150" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" s="10" t="inlineStr"/>
+    </row>
+    <row r="44" ht="150" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>★C6</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>Q2/Q5</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>「戦略依存×Must/Should/Could」の4象限と二層整理（共通要件＋テーマ別シナリオ）を適用した過去案件で、①線引きの判断が貴社とクライアントで割れた実例と収拾方法、②戦略確定後に実際にRFP要件がどれだけ変わったか（変更件数・変更率）を教えてください。</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>書面で最高評価（Q2素点5）をつけた中核方法論の実効性検証。素点5は「裏付け完全」が要件のため、高得点ほど質疑での検証が必須。方法論が本当に手戻りを減らしたのかをアウトカム（変更率）で証明させる。</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F44" s="9" t="inlineStr">
         <is>
           <t>良: 割れた実例を率直に語り、変更率を数字で示せる（例: 戦略確定後の要件変更が全体の○%に収まり、うち構造変更はゼロ等）。
 危: 「うまくいきました」のみで数字なし。割れた実例が「ない」（適用実績が浅いか、都合の悪い情報を出さない）。</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G44" s="9" t="inlineStr">
         <is>
           <t>本件でMust×戦略非依存の「骨格」に置くと仰る組織マスタ・証憑統制・Scope1/2算定のうち、実は当社の戦略次第で動き得るものはどれですか。骨格の線引きを最初の何週で当社と合意しますか。</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H44" s="9" t="inlineStr">
         <is>
           <t>変更率のデータがないなら、「手戻り最小化」の効果は測定されていない主張になります。本件では何をもって「手戻りが最小化された」と評価すればよいか、測定可能な形で定義してください。</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr"/>
-      <c r="J42" s="10" t="inlineStr"/>
-    </row>
-    <row r="43" ht="150" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr"/>
+      <c r="J44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45" ht="150" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>★C7</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>C1/C2</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>当社にて成果物を照合したところ、PwC社の27,000,000円の見積り（3.6ヶ月）には「開示効率化検討」「展開計画・定着計画」「PJ計画書」が含まれていますが、貴社の基本スコープ5,300万円（3.9ヶ月）にはこれらが含まれず、オプションBに切り出されています。つまり貴社の基本スコープは他社より成果物が狭いにもかかわらず、価格はPwC社の約2倍です。この差の主因は単価水準ですか、投入人数ですか。ランク別内訳（C1の宿題回答）でご説明ください。</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>最も鋭い一問。品質でもスコープでも説明のつかない価格差（超過コスト）を、貴社自身に他社比較で直接答えさせる。回避不能な形で単価水準の説明責任を負わせる。</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>良: 単価が他社より高い理由を明確に説明（シニアリティ、専門性、リスクプレミアム等）し、その根拠を具体的な数字・実例で示す。
 危: 「価値が違います」等の定性論で数字を出さない。他社見積りの前提を問題にして自社の説明を回避する。</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>その単価差に見合う成果（例: 手戻りゼロ、保証人指摘ゼロ）を過去案件で実現した実例はありますか。本件でその成果を測定可能な形で契約に落とし込めますか。</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t>説明できないなら、貴社の基本スコープ価格は市場価格から外れている可能性があります。PwC社の27,000,000円の内容に貴社の強み（2段階アーキテクチャ・独立データ要件定義書）を追加した場合の増分見積りを、この場で概算で示してください。</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr"/>
-      <c r="J43" s="10" t="inlineStr"/>
-    </row>
-    <row r="44" ht="150" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr"/>
+      <c r="J45" s="10" t="inlineStr"/>
+    </row>
+    <row r="46" ht="150" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>★C8</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>Q3/Q4/Q6</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>アドバイザーの森銅様は、SSBJ対応向けシステム要件定義・導入実績（物流業・化学メーカー・非鉄金属メーカー等）を複数お持ちと理解しています。この方の本件での実稼働率は体制表で「適宜」とありますが、具体的に週何時間、基本スコープのどのタスク（#4システム構成案策定・#8システム要件定義等）を担当されますか。また、攻め側（#2出口設計のユースケース優先順位付け）を主導するのはどなたですか、その方の類似実績を教えてください。</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>貴社の体制で最もシステム連携・SSBJシステム導入の実務経験が濃い人物（森銅様）が「適宜」という低稼働の位置づけになっている。守り担当（森銅様）と攻め担当が明確に分かれているか、それぞれの実働時間を具体的に確認する。</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="F46" s="9" t="inlineStr">
         <is>
           <t>良: 森銅様の週次稼働時間とタスク対応を具体的に提示し、攻め担当者（別人物）の実例も明示。
 危: 「必要に応じて随時サポートします」（稼働時間・タスク対応が不明確）。</t>
         </is>
       </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="G46" s="9" t="inlineStr">
         <is>
           <t>森銅様が「適宜」ではなく特定タスク（#4・#8等）に固定的にコミットする形に変更できますか。その場合の稼働率%と体制表の更新版を提出してください。</t>
         </is>
       </c>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="H46" s="9" t="inlineStr">
         <is>
           <t>「適宜」のままだと、基本スコープの技術的な品質は山野様（マネージャー）と平野様（シニアコンサルタント）と貴社選定のコンサルタント3名（人数調整）に依存することになります。この体制でシステム構成案（#4）の技術的妥当性を担保できる根拠を示してください。</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr"/>
-      <c r="J44" s="10" t="inlineStr"/>
-    </row>
-    <row r="45" ht="150" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr"/>
+      <c r="J46" s="10" t="inlineStr"/>
+    </row>
+    <row r="47" ht="150" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>★C9</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>即答</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>Q1/Q2</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>貴社提案書には、難所①（ルールの策定）について、業務要件検討の前提として「事前にLION様にて策定済みと想定」（P.28）とする記述と、出口設計（#2）でMust/Should/Could×戦略依存の6象限により線引き合意を最上流の意思決定点に設計する（P.26）という記述の両方が存在します。難所①は貴社が能動的に検討・確定を主導するのか、それとも当社が既に確定済みという前提で臨むのか、どちらですか。</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>提案書内の矛盾を解消する。前提化（L0）なら難所①は実質スコープに含まれず、方法論適用（L2〜L3）なら含まれる——この違いはQ1・Q2の確定素点、および「なぜこの作業が53,000,000円の基本スコープに入っているか」という価格妥当性の双方に影響する。</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>良: 「制度上確定済みの部分（組織境界の一次案等）は前提とし、戦略変動に応じた線引き調整の部分は6象限方法論で能動的に検討する」等、前提とする部分と方法論で検討する部分の境界を明確に整理できる。
 危: 矛盾を認めない、または矛盾自体に気づいていない。</t>
         </is>
       </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>前提とする部分と方法論で検討する部分の境界線を、今この場で具体的に示してください。当社が「策定済み」と誤解している範囲はどこですか。</t>
         </is>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="H47" s="9" t="inlineStr">
         <is>
           <t>矛盾を解消できないなら、貴社は難所①への対応方針を固めきれていないことになります。この状態のまま、当社は53,000,000円の基本スコープの妥当性をどう判断すればよいですか。</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr"/>
-      <c r="J45" s="10" t="inlineStr"/>
+      <c r="I47" s="10" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A36:J36"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A25:J25"/>
   </mergeCells>

--- a/docs/コンペ質疑_質問票.xlsx
+++ b/docs/コンペ質疑_質問票.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検（第1回）で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。⑦アビームv1.1改訂（基本/オプション分離）と成果物カバレッジ照合（第2回再点検）を反映しC1・★A7・★B6・★C7を追加/更新。スコープ差は双方向（アビームが広い部分／PwC案②が広い部分の両方が存在）のため、価格差を単純にスコープや品質だけで説明させない設計。⑧第3回再点検: アサインメンバーの経歴を「攻め／守り」の技術専門性（システム連携・API連携経験等）で照合し、★共8・★A8・★B7・★C8を追加。Q6は実名・経歴の有無までしか採点していないため、本件の技術判断に耐える経験の有無と、その人物が実働で入るか（アドバイザー止まりでないか）を別途確認する。⑨第4回再点検: 5つの難所（貴社RFP由来の共通言語）×深さレベル（L0前提化〜L4詳細設計）×担当で3社を独立照合した結果を踏まえ、★共9（自己採点による照合）・★A9（ライズの深さの天井を即答で検証）・★B8（PwCの前提化・後ろ倒しが戦略判断か能力の限界か）・★C9（アビーム提案書内の難所①に関する記述矛盾の解消）を追加。⑩第5回再点検: 弊社依頼事項（攻め・守り）とPwC提案書を1行ずつ照合した結果、PwC自身が「ご依頼事項（PwC理解）」（P.10）で正確に理解を示している『攻め』の2本柱（Scope3一次データ改革・CFP開示スキーム）が、実行計画（P.28）では両方ともStep2以降に後ろ倒しになっている自己矛盾を発見。★B9（この矛盾を直接突く）・★B10（自ら追加提起した難所⑦と実行タスクの深さの不釣り合いを突く）を追加。⑪第6回再点検: P.39「アプローチ想定作成物」の図面を精査した結果、①攻め系の成果物ボックスが図全体に1つも存在せず★B9の指摘を構造面で裏付け、②新業務定着の箱が2つのみで★B10を裏付け、③「提案スコープ」点線の境界（開示戦略策定・RFP作成・アーキテクチャ素案が内外どちらか）が判読困難、④RFP作成が全ワークストリームの統合点＝クリティカルパス集中構造、という新たな発見。③④について★B11・★B12を追加。</t>
+          <t>使い方: ①宿題型（緑）は質疑1週間前に送付し書面回答を回収 ②即答型（橙）は当日、資料参照なしで従事予定者本人に回答させる ③主質問の回答を聞いたら、回答の質に応じて「深掘り質問（回答が具体的な場合）」または「追い込み質問（回答が曖昧・回避的な場合）」で必ず一段深く踏み込む ④回答メモ欄に当日記入し、質疑後48時間以内に「確定素点への反映」欄を埋めて採点表を更新する。共通質問は3社に同じ順番で実施し、回答の具体度を相対比較する。 ⑤★印は攻め/守り・採点カバレッジ再点検（第1回）で追加した質問（攻め＝Q4/C4、および高得点素点5の検証用）。⑥採点規律: 回答は必ず「関連採点項目」の素点にのみ反映する。採点項目に紐づかない印象で総合評価を動かさない。⑦アビームv1.1改訂（基本/オプション分離）と成果物カバレッジ照合（第2回再点検）を反映しC1・★A7・★B6・★C7を追加/更新。スコープ差は双方向（アビームが広い部分／PwC案②が広い部分の両方が存在）のため、価格差を単純にスコープや品質だけで説明させない設計。⑧第3回再点検: アサインメンバーの経歴を「攻め／守り」の技術専門性（システム連携・API連携経験等）で照合し、★共8・★A8・★B7・★C8を追加。Q6は実名・経歴の有無までしか採点していないため、本件の技術判断に耐える経験の有無と、その人物が実働で入るか（アドバイザー止まりでないか）を別途確認する。⑨第4回再点検: 5つの難所（貴社RFP由来の共通言語）×深さレベル（L0前提化〜L4詳細設計）×担当で3社を独立照合した結果を踏まえ、★共9（自己採点による照合）・★A9（ライズの深さの天井を即答で検証）・★B8（PwCの前提化・後ろ倒しが戦略判断か能力の限界か）・★C9（アビーム提案書内の難所①に関する記述矛盾の解消）を追加。⑩第5回再点検: 弊社依頼事項（攻め・守り）とPwC提案書を1行ずつ照合した結果、PwC自身が「ご依頼事項（PwC理解）」（P.10）で正確に理解を示している『攻め』の2本柱（Scope3一次データ改革・CFP開示スキーム）が、実行計画（P.28）では両方ともStep2以降に後ろ倒しになっている自己矛盾を発見。★B9（この矛盾を直接突く）・★B10（自ら追加提起した難所⑦と実行タスクの深さの不釣り合いを突く）を追加。⑪第6回再点検: P.39「アプローチ想定作成物」の図面を精査した結果、①攻め系の成果物ボックスが図全体に1つも存在せず★B9の指摘を構造面で裏付け、②新業務定着の箱が2つのみで★B10を裏付け、③「提案スコープ」点線の境界（開示戦略策定・RFP作成・アーキテクチャ素案が内外どちらか）が判読困難、④RFP作成が全ワークストリームの統合点＝クリティカルパス集中構造、という新たな発見。③④について★B11・★B12を追加。⑫第7回再点検: 弊社依頼事項（攻め・守り）とアビーム提案書を照合した結果、アビームの提案コンセプト（P.3、①特殊前提対応②守りの設計③攻めの設計）とP.2の目的整理（守り＝証明できる体制、攻め＝企業価値向上）に対し、その『証明』を担う成果物（内部統制設計方針書#12・効果試算#15）が両方ともオプションBに切り出されているという、PwCと同型でより本質的な矛盾を発見。★C10（この矛盾を直接突く）・★C11（保証人協議の成果物断絶リスク）を追加。</t>
         </is>
       </c>
     </row>
@@ -2475,6 +2475,96 @@
       </c>
       <c r="I47" s="10" t="inlineStr"/>
       <c r="J47" s="10" t="inlineStr"/>
+    </row>
+    <row r="48" ht="150" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>★C10</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Q1/Q3/Q4</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>貴社の提案コンセプト（P.3）は、①特殊前提への対応、②守りの設計（インプットの極小化と強固なガバナンスの確立）、③攻めの設計（アウトカムの最大化）の3本柱で構成されています。また、当社のプロジェクト目的整理（P.2）では、『守り』を『システムで客観的に証明できる状態ができる体制の構築』、『攻め』を『企業価値向上の実現』と定義いただいています。一方、その『証明できる体制』の中核となる内部統制設計方針書・キーコントロール定義（貴提案#12）、および企業価値向上を証明する効果試算・経営報告支援（貴提案#15）は、いずれも基本スコープ（5,300万円）ではなく、オプションB（2,200万円）に含まれています。基本スコープだけでは、貴社ご自身が定義された『守り』『攻め』の目的——すなわち成果を客観的に証明する部分——を達成できないという理解でよろしいでしょうか。</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>PwC社に指摘した『依頼理解と実行計画の矛盾』と同じ構造を、貴社の提案コンセプトそのものに見出した、今回最も本質的な一問。貴社の3本柱のうち②③の『証明工程』がいずれもオプション化されており、基本スコープは『設計・識別』までで『証明』は別料金という構造になっている可能性がある。</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>良: 『基本スコープは要件定義フェーズとして設計・識別までを行い、証明文書の本格作成は投資判断の材料が固まった後（Option B）に行う方が合理的』等、段階分けの妥当性を明確に説明できる。
+危: 矛盾を認めず「基本スコープでも十分に守り・攻めは実現されます」と言い切る、または段階分けの理由を説明できない。</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>段階分けが合理的だとしても、当社が11月末までに経営会議で守り・攻め双方の投資判断を行うためには証明文書（内部統制設計方針書・効果試算）が必要です。オプションBを基本スコープと同時並行で実施した場合、追加でどの程度の期間・体制が必要になりますか。</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>証明工程がオプション化されている理由が明確でないなら、貴社の提案コンセプト（P.3）は基本スコープの実態よりも大きく見せている可能性があります。5,300万円の基本スコープで実際に『証明できる』のは、守り・攻めのうちどの部分までか、この場で明確に切り分けてください。</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr"/>
+      <c r="J48" s="10" t="inlineStr"/>
+    </row>
+    <row r="49" ht="150" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>★C11</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>即答</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Q3/D2</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>保証人との事前協議（貴提案#12の一部）は基本スコープに含まれる一方、その協議結果を反映する内部統制設計方針書・承認フロー定義書の作成はオプションBに含まれています。基本スコープの期間中に保証人協議を実施しても、その結果を文書に落とし込む作業がオプションBとして別途契約されない限り、協議の成果が書面化されないまま基本スコープが完了する可能性があります。基本スコープ完了時点で、保証人協議の内容はどのような形で記録され、当社に引き継がれますか。</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>業務プロセスの断絶リスクを検証する。「協議はしたが、成果は書面化されない」という状態を防ぐための具体的な引継ぎ方法を確認する。</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>良: 協議の議事録・論点整理を基本スコープの成果物として明示的に残す設計になっている。
+危: 「口頭での共有に留まります」等、正式な記録が基本スコープの成果物として定義されていない。</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>その議事録・論点整理は、当社が後日保証人と再度協議する際にそのまま使える形式で提供されますか。</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>正式な記録が基本スコープの成果物として残らないのであれば、当社はオプションBを追加発注しない限り、保証人協議の成果を実務で活用できないことになります。それでも基本スコープに証憑事前協議を含める理由を教えてください。</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr"/>
+      <c r="J49" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
